--- a/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Frasningskonsistens lärandemål" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens lärandemål'!$A$1:$E$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$288</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E206"/>
+  <dimension ref="A1:E288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -482,12 +482,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:         - Uppskatta värmebehov för lågenergibyggnader i kallt klimat och rel…</t>
+          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -509,12 +509,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:         - Förbereda och genomföra energisimuleringar i byggnader.     - Identif…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -536,12 +536,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenterna kunna:    - genomföra fältmätningar av utomhusklimat    - inhämta, bearbeta och p…</t>
+          <t>Avviker från gold standard: Efter genomgången kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs ska studenterna kunna:    - Samla in, sammanställa och analysera information från olika källor för at…</t>
+          <t>Avviker från gold standard: Efter godkänd kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -590,12 +590,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:       - förklara vad hållbar utveckling innebär för byggande och boende    -…</t>
+          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -617,12 +617,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska skaffa sig kunskaper inom samhällsplanering, byggandets regelverk…</t>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska skaffa sig kunskaper inom samhällsplanering, byggandets regelverk…</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs skall studenten kunna:       - beskriva en väg- respektive bankonstruktions uppbyggnad och redogöra…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -671,12 +671,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper inom värme- och fukttransport, ljudisoleri…</t>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper inom värme- och fukttransport, ljudisoleri…</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten efter genomgången kurs ska kunna rita en 3D-husmodell.      Efter gen…</t>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten efter genomgången kurs ska kunna rita en 3D-husmodell.      Efter gen…</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -725,12 +725,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten skall skaffa sig kunskaper om såväl teoretisk som praktisk träbyggnad…</t>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten skall skaffa sig kunskaper om såväl teoretisk som praktisk träbyggnad…</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet me kursen är att studenten ska skaffa sig kunskaper och färdigheter om systemuppbyggnad och funkt…</t>
+          <t>Avviker från gold standard: Det övergripande målet me kursen är att studenten ska skaffa sig kunskaper och färdigheter om systemuppbyggnad och funkt…</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -779,12 +779,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att kursdeltagaren ska skaffa sig grundläggande kunskaper om BIM (Byggnadsinformati…</t>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att kursdeltagaren ska skaffa sig grundläggande kunskaper om BIM (Byggnadsinformati…</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -806,12 +806,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med examensarbetet är att studenten inom givna ramar ska utföra ett arbete av utvecklingskaraktär…</t>
+          <t>Avviker från gold standard: Det övergripande målet med examensarbetet är att studenten inom givna ramar ska utföra ett arbete av utvecklingskaraktär…</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska uppnå förmåga att med helhetssyn självständigt och kreativt ident…</t>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska uppnå förmåga att med helhetssyn självständigt och kreativt ident…</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse_  Efter avslutad kurs ska studenten kunna:    - redogöra för lämpliga sätt att problematisera, f…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse_  Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -887,12 +887,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Vid design av energieffektiva byggnader med hög nivå av komfort och hållbarhet krävs både en djup kunskap om detaljer so…</t>
+          <t>Avviker från gold standard: Vid design av energieffektiva byggnader med hög nivå av komfort och hållbarhet krävs både en djup kunskap om detaljer so…</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursen fokuserar på miljöklassningsverktyg för byggnader. Efter avslutad kurs ska studenterna kunna:      - Visa förståe…</t>
+          <t>Avviker från gold standard: Kursen fokuserar på miljöklassningsverktyg för byggnader. Efter avslutad kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -941,12 +941,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenterna kunna:    - Ställa samman, analysera och kombinera information från olika källor för…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten efter genomgången kurs ska kunna rita en 3D-modell.      Efter genomg…</t>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten efter genomgången kurs ska kunna rita en 3D-modell.      Efter genomg…</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -995,12 +995,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska skaffa sig grundläggande kunskaper om BIM (Byggnadsinformationsmo…</t>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska skaffa sig grundläggande kunskaper om BIM (Byggnadsinformationsmo…</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska skaffa sig grundläggande kunskaper inom fysisk planering med tyng…</t>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska skaffa sig grundläggande kunskaper inom fysisk planering med tyng…</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska skaffa sig kunskaper i husbyggnad, speciellt beträffande planering, utform…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att studenten ska skaffa sig kunskaper i husbyggnad, speciellt beträffande planering, utform…</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper om laster och krafter i byggkonstruktioner…</t>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper om laster och krafter i byggkonstruktioner…</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper för att kunna organisera och genomföra pro…</t>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper för att kunna organisera och genomföra pro…</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper i husbyggnadsteknik, speciellt beträffande…</t>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper i husbyggnadsteknik, speciellt beträffande…</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet är att studenten skall tillägna sig kunskaper om laster och krafter i byggkonstruktioner samt gru…</t>
+          <t>Avviker från gold standard: Det övergripande målet är att studenten skall tillägna sig kunskaper om laster och krafter i byggkonstruktioner samt gru…</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper om byggandets organisation och genomförand…</t>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper om byggandets organisation och genomförand…</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:       - redogöra för vad som styr det termiska inomhusklimatet    - redogöra…</t>
+          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska tillägna sig kunskap och förståelse om fastighetsföretagens förutsättninga…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att studenten ska tillägna sig kunskap och förståelse om fastighetsföretagens förutsättninga…</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:    - redogöra för anbuds- och produktionsprocessen     - redogöra för svensk…</t>
+          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten skall tillägna sig grundläggande kunskaper i arbetsplatsens organisat…</t>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten skall tillägna sig grundläggande kunskaper i arbetsplatsens organisat…</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       - visa förståelse för byggnadskonstruktioners funktion och säkerhet…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att öka medvetenheten om de hållbarhetsutmaningar som vi står inför. Kursen avser a…</t>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att öka medvetenheten om de hållbarhetsutmaningar som vi står inför. Kursen avser a…</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1373,12 +1373,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska skaffa sig kunskaper i husbyggnadsteknik, speciellt beträffande u…</t>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska skaffa sig kunskaper i husbyggnadsteknik, speciellt beträffande u…</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       - beskriva och utföra kulturhistorisk värdering av befintlig bebygge…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GBY34M</t>
+          <t>GBY342</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1427,24 +1427,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs skall den studerande kunna:    - identifiera ett intressant område/ämne att undersöka och formulera e…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY342</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GBY34N</t>
+          <t>GBY34B</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1454,24 +1454,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs skall studenten kunna:    - identifiera ett vetenskapligt intressant område samt formulera och unders…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34B</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GBY3AX</t>
+          <t>GBY34M</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1481,1077 +1481,1077 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande för ett konkret husbyggnadsprojekt kunna:       - välja byggtekniska lösningar fö…</t>
+          <t>Avviker från gold standard: Efter godkänd kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY3AX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34M</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GDT2JM</t>
+          <t>GBY34N</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DTA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs skall studenten kunna:      - Redogöra för historik och utveckling av system för datakommunikation s…</t>
+          <t>Avviker från gold standard: Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34N</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GDT2JN</t>
+          <t>GBY36S</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DTA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs skall studenten kunna:      - Redogöra för, och värdera, hierarkiska konvergerade nätverksdesigner…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY36S</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GDT34Z</t>
+          <t>GBY37D</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DTA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs skall studenten kunna:    - beskriva hur teknik som virtualisering, mjukvarupaketering via containerb…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT34Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY37D</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>ET1029</t>
+          <t>GBY38D</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:          - Redogöra för grundläggande principer i styrteknik.    - Redogör…</t>
+          <t>Avviker från gold standard: Efter godkänd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ET1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY38D</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>BFY224</t>
+          <t>GBY38E</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska tillägna sig kunskap om vetenskapligt arbetssätt inom naturvetenskap…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY224</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY38E</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>FY1018</t>
+          <t>GBY3AX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Studenten skall efter genomgången kurs kunna        - redogöra för termodynamikens grundbegrepp    - formulera och lösa…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande för ett konkret husbyggnadsprojekt kunna:…</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FY1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY3AX</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GIE26L</t>
+          <t>GBY3DW</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse_   Efter avslutad kurs ska studenten kunna:       - redogöra för grundläggande begrepp och metod…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY3DW</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GIE26M</t>
+          <t>GBY3DX</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse_   Efter avslutad kurs skall studenten kunna:     - redogöra för grundläggande begrepp inom orga…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY3DX</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GIE26N</t>
+          <t>GDT2JM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>DTA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse_   Efter avslutad kurs ska studenten kunna:         - redogöra för centrala begrepp inom kvalite…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JM</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GIE26P</t>
+          <t>GDT2JN</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>DTA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse    _Efter avslutad kurs ska studenten kunna        - redogöra för grundläggande begrepp och föru…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JN</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GIE29N</t>
+          <t>GDT34Z</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>DTA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna       - redogöra för projektledarens roll och ansvar…</t>
+          <t>Avviker från gold standard: Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE29N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT34Z</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GIE2L7</t>
+          <t>GDT3CR</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>DTA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse    _Efter avslutad kurs ska studenten kunna    - redogöra för den historiska framväxten av Lean.…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2L7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT3CR</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GIE2MF</t>
+          <t>ET1029</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna:    - redogöra översiktligt för utvecklingen från tra…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2MF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ET1029</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GIE2QS</t>
+          <t>GET36T</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Avvikande introfras: **Kunskap och förståelse**  Efter avslutad kurs ska studenten kunna:    - redogöra översiktligt för processorienterad ve…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2QS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GET36T</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GIE2RF</t>
+          <t>BFY224</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse_      Efter genomgången kurs ska studenten kunna:    - visa fördjupad kunskap inom ett valt områ…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska tillägna sig kunskap om vetenskapligt arbetssätt inom naturvetenskap …</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2RF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY224</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>IE1068</t>
+          <t>BFY225</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna:    - redogöra för lämpliga sätt att problematisera,…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY225</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>IE1069</t>
+          <t>BFY226</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse_   Efter avslutad kurs ska studenten kunna:       - redogöra för grundläggande begrepp och metod…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY226</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>IE1076</t>
+          <t>BFY227</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse    _Efter avslutad kurs ska studenten kunna        - redogöra för grundläggande begrepp och föru…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1076</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY227</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>IE2003</t>
+          <t>FY1018</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Avvikande introfras: De allmänna målen med examensarbetet är att ge kursdeltagarna möjligheter att utveckla sin förmåga att inom ämnet indust…</t>
+          <t>Avviker från gold standard: Studenten skall efter genomgången kurs kunna…</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FY1018</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>AIK232</t>
+          <t>GFY345</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna:         - redogöra för centrala begrepp inom området…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFY345</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GIK23M</t>
+          <t>GIE26L</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse_   Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK23M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26L</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GIK289</t>
+          <t>GIE26M</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna:      - förklara vad begreppet objektorientering inne…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse_   Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26M</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GIK28T</t>
+          <t>GIE26N</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna      _Kunskap och förståelse_    - Redogöra för val av forskningsansats i r…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse_   Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26N</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GIK299</t>
+          <t>GIE26P</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper och färdigheter i att utveckla prog…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse    _Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK299</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26P</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GIK29B</t>
+          <t>GIE29N</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:          - Förklara relevanta begrepp och terminologi inom programutveckling.…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK29B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE29N</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GIK2AL</t>
+          <t>GIE2L7</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse    _Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2L7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GIK2BD</t>
+          <t>GIE2MF</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse    Efter avslutad kurs ska den studerande kunna       - Beskriva projektstyrningsmodeller, dess f…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2BD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2MF</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GIK2FB</t>
+          <t>GIE2QS</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska studenten kunna:    - Beskriva ofta förekommande begrepp inom artificiel…</t>
+          <t>Avviker från gold standard: **Kunskap och förståelse**  Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2FB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2QS</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GIK2JX</t>
+          <t>GIE2RF</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Avvikande introfras: **Kunskap och förståelse   **Efter avslutad kurs ska studenten kunna:    - Redogöra för grundläggande teorier beträffand…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse_      Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2JX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2RF</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GIK2KM</t>
+          <t>GIE36Y</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att använda och utveckla mju…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2KM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE36Y</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GIK2LF</t>
+          <t>GIE36Z</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse   _Efter avslutad kurs ska den studerande kunna    - beskriva lagar som reglerar användning av d…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2LF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE36Z</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GIK2NV</t>
+          <t>GIE372</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att hantera data över ett da…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE372</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GIK2NX</t>
+          <t>GIE3FW</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig kunskaper och färdigheter i att samla in och bearbeta data…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3FW</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GIK2PB</t>
+          <t>GIE3H2</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska tillägna sig kunskap om och förståelse för systemförvaltning och test…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3H2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GIK2PD</t>
+          <t>GIE3JW</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att introducera studenten till nätverk, nätverkstjänster , nätverkssäkerhet, datakommunikati…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3JW</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GIK2PF</t>
+          <t>IE1068</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet är att studenterna förvärvar fördjupade kunskaper och färdigheter inom IT-arkitektur som omfattar…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1068</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GIK2PG</t>
+          <t>IE1069</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenter i grupp i ett systemutvecklingsprojekt planerar, analyserar, designar…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse_   Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1069</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GIK2Q3</t>
+          <t>IE1076</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:    _   Kunskap och förståelse_    - Förklara begrepp och terminologi relaterade…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse    _Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2Q3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1076</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GIK2QZ</t>
+          <t>IE2003</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse_     Efter avslutad kurs ska studenten kunna:       - redogöra för begrepp inom visuell kommunik…</t>
+          <t>Avviker från gold standard: De allmänna målen med examensarbetet är att ge kursdeltagarna möjligheter att utveckla sin förmåga att inom ämnet indust…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2QZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE2003</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GIK2UK</t>
+          <t>AIK232</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse   Efter genomförd kurs skall studenten kunna:    - använda verktyg och funktioner som är centrala…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2UK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GIK2V4</t>
+          <t>GIK23M</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2588,24 +2588,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att introducera studenten till cybersäkerhetstrender, hotbilder vid IT-användning mot person…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda …</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2V4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK23M</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GIK2XJ</t>
+          <t>GIK289</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2615,24 +2615,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse    Efter avslutad kurs ska studenten kunna:     - redogöra för de teoretiska grunderna inom objek…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK289</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GIK2XK</t>
+          <t>GIK28T</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2642,24 +2642,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Avvikande introfras: **Kunskap och förståelse**   Efter avslutad kurs ska den studerande kunna:    - redogöra för centrala begrepp, metoder o…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna      _Kunskap och förståelse_…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GIK2XZ</t>
+          <t>GIK299</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2669,24 +2669,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Avvikande introfras: **Kunskap och förståelse   **Efter avslutad kurs ska den studerande kunna:       - beskriva metoder, modeller, roller oc…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper och färdigheter i att utveckla prog…</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK299</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GIK2YK</t>
+          <t>GIK29B</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2696,24 +2696,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse   _Efter godkänd kurs ska den studerande kunna:    - förklara normaliseringens betydelse för en…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK29B</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GIK2YL</t>
+          <t>GIK2AL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2723,24 +2723,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse   _Efter godkänd kurs ska den studerande kunna:    - redogöra för metoder och modeller inom proj…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda …</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2AL</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GIK2YN</t>
+          <t>GIK2BD</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2750,24 +2750,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse   _Efter godkänd kurs ska den studerande kunna:    - redogöra för grundläggande begrepp inom obj…</t>
+          <t>Avviker från gold standard: Kunskap och förståelse    Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2BD</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GIK2YP</t>
+          <t>GIK2FB</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2777,24 +2777,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse_   Efter godkänd kurs ska den studerande kunna:    - förklara renderingsprocessen för HTML (Hype…</t>
+          <t>Avviker från gold standard: Kunskap och förståelse  Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2FB</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GIK2YR</t>
+          <t>GIK2JX</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2804,24 +2804,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse   Efter godkänd kurs ska den studerande kunna:    - använda centrala begrepp och principer inom d…</t>
+          <t>Avviker från gold standard: **Kunskap och förståelse   **Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2JX</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GIK32K</t>
+          <t>GIK2KM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2831,24 +2831,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Saknar kolon</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Saknar kolon: `Efter godkänd kurs ska studenten kunna`</t>
+          <t>Avviker från gold standard: Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att använda och utveckla mju…</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2KM</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GIK32L</t>
+          <t>GIK2LF</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2858,24 +2858,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Saknar kolon</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Saknar kolon: `Efter godkänd kurs ska studenten kunna`</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse   _Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2LF</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GIK32M</t>
+          <t>GIK2NV</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2885,24 +2885,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Saknar kolon</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Saknar kolon: `Efter godkänd kurs ska studenten kunna`</t>
+          <t>Avviker från gold standard: Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att hantera data över ett da…</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NV</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GIK32N</t>
+          <t>GIK2NX</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2912,24 +2912,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Saknar kolon</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Saknar kolon: `Efter godkänd kurs ska studenten kunna`</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande tillägnar sig kunskaper och färdigheter i att samla in och bearbeta data …</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NX</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GIK339</t>
+          <t>GIK2PB</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2939,24 +2939,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse_   Efter avslutad kurs ska studenten kunna:    - redogöra för grundläggande begrepp inom webbutv…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska tillägna sig kunskap om och förståelse för systemförvaltning och test…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK339</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PB</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GIK347</t>
+          <t>GIK2PD</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2966,24 +2966,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse    _Efter godkänd kurs ska den studenten kunna    - använda centrala begrepp inom interaktionsde…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att introducera studenten till nätverk, nätverkstjänster , nätverkssäkerhet, datakommunikati…</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK347</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PD</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>IK1032</t>
+          <t>GIK2PF</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2993,24 +2993,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Målet med examensarbetet är att studenten ska förvärva fördjupade kunskaper inom examensarbetets ämnesområde genom att u…</t>
+          <t>Avviker från gold standard: Det övergripande målet är att studenterna förvärvar fördjupade kunskaper och färdigheter inom IT-arkitektur som omfattar…</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PF</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>IK1064</t>
+          <t>GIK2PG</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3020,24 +3020,24 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska tillägna sig utökade kunskaper i objektorienterad programmering och m…</t>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenter i grupp i ett systemutvecklingsprojekt planerar, analyserar, designar…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PG</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>IK1066</t>
+          <t>GIK2Q3</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3047,2965 +3047,5179 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig fördjupade kunskaper och färdigheter inom ämnesområdet geno…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:    _   Kunskap och förståelse_…</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2Q3</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GMA28W</t>
+          <t>GIK2QZ</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska öka sin förmåga att förstå och använda grundläggande matematiska…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse_     Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA28W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2QZ</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GMA2EY</t>
+          <t>GIK2UK</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:       - utföra numeriska beräkningar med tal i t ex decimalform, bråkform och p…</t>
+          <t>Avviker från gold standard: Kunskap och förståelse   Efter genomförd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2UK</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>MA0011</t>
+          <t>GIK2V4</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.  Efter avslutad kurs skall stud…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att introducera studenten till cybersäkerhetstrender, hotbilder vid IT-användning mot person…</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2V4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>MA0013</t>
+          <t>GIK2XJ</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.  Efter avslutad kurs skall stud…</t>
+          <t>Avviker från gold standard: Kunskap och förståelse    Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XJ</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>MA1040</t>
+          <t>GIK2XK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska utveckla sin förmåga att förstå och använda matematiska begrepp o…</t>
+          <t>Avviker från gold standard: **Kunskap och förståelse**   Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1040</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XK</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>MA1042</t>
+          <t>GIK2XZ</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenterna skall tillägna sig grundläggande teoretiska kunskaper i elementär a…</t>
+          <t>Avviker från gold standard: **Kunskap och förståelse   **Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XZ</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>AMD238</t>
+          <t>GIK2YK</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande visar sådana fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs fö…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse   _Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YK</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GMD2BH</t>
+          <t>GIK2YL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:      - redogöra för och problematisera, såväl skriftligt som muntligt, mat…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse   _Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YL</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GMD2EX</t>
+          <t>GIK2YN</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:      - redogöra för olika sätt att formulera och lösa matematiska uppgifte…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse   _Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2EX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YN</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GMD2GU</t>
+          <t>GIK2YP</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:      - redogöra för och problematisera, såväl muntligt som skriftligt, mat…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse_   Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YP</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GMD2H2</t>
+          <t>GIK2YR</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - visa kännedom om och använda matematikens grundläggande språk oc…</t>
+          <t>Avviker från gold standard: Kunskap och förståelse   Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YR</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GMD2H3</t>
+          <t>GIK32J</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:      - genomföra och diskutera en statistisk undersökning med relevans uti…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32J</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GMD2H4</t>
+          <t>GIK32K</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - visa kännedom om definitioner och satser i euklidisk geometri,    - b…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse _  Efter godkänd kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32K</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GMD2H5</t>
+          <t>GIK32L</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - förstå begreppet funktion inklusive invers, bijektion samt monoton fu…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse _  Efter godkänd kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32L</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GMD2HE</t>
+          <t>GIK32M</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - identifiera och reflektera kring matematikdidaktiska begrepp, teorier…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse _  Efter godkänd kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32M</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GMD2HF</t>
+          <t>GIK32N</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - problematisera matematikdidaktiska begrepp, teorier och perspektiv om…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse _  Efter godkänd kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32N</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GMD2HG</t>
+          <t>GIK339</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - utifrån matematikdidaktiska ramverk, teorier och perspektiv analysera…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse_   Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK339</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GMD2HH</t>
+          <t>GIK346</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - identifiera och reflektera kring matematikdidaktiska begrepp, teorier…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK346</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GMD2HJ</t>
+          <t>GIK347</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - problematisera matematikdidaktiska begrepp, teorier och perspektiv om…</t>
+          <t>Avviker från gold standard: _Kunskap och förståelse    _Efter godkänd kurs ska den studenten kunna…</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK347</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GMD2HK</t>
+          <t>GIK348</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - utifrån matematikdidaktiska ramverk, teorier och perspektiv analysera…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK348</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GMD2MH</t>
+          <t>GIK34Y</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:      - genomföra och diskutera en statistisk undersökning med relevans uti…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK34Y</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GMD2MJ</t>
+          <t>GIK373</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - förstå begreppet funktion inklusive invers, bijektion samt monoton fu…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK373</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GMD2PA</t>
+          <t>GIK38G</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - med grund i aktuella styrdokument, litteratur och undervisningsmateri…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2PA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK38G</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GMD3GZ</t>
+          <t>GIK38H</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för och problematisera, såväl skriftligt som muntligt, matem…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD3GZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK38H</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>MD1085</t>
+          <t>IK1032</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:     - redogöra för och problematisera olika teoretiska perspektiv inom spe…</t>
+          <t>Avviker från gold standard: Målet med examensarbetet är att studenten ska förvärva fördjupade kunskaper inom examensarbetets ämnesområde genom att u…</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1032</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>MD1097</t>
+          <t>IK1064</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna       - redogöra för matematikens utveckling i stora drag, genom historien…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska tillägna sig utökade kunskaper i objektorienterad programmering och m…</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1064</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>MD1098</t>
+          <t>IK1066</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:      - redogöra  för olika vetenskapliga teorier och forskningsrön som beh…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande tillägnar sig fördjupade kunskaper och färdigheter inom ämnesområdet geno…</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1066</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>MD1103</t>
+          <t>GMA28W</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för olika vetenskapliga teorier och forskningsrön såväl nati…</t>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska öka sin förmåga att förstå och använda grundläggande matematiska …</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1103</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA28W</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>MD2023</t>
+          <t>GMA2EY</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - beskriva, analysera, diskutera och tillämpa differentialekvationer  a…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>MD2024</t>
+          <t>GMA2ZS</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - beskriva, analysera, diskutera och tillämpa aritmetik, mängdlära,  bi…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2ZS</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>MD2025</t>
+          <t>GMA2ZT</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:      - lösa linjära ekvationssystem med matriser    - uttrycka linjer, pla…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2ZT</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>MD2026</t>
+          <t>GMA33Z</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - lösa differentialekvationer av första ordningen, separabla differenti…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA33Z</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GMT228</t>
+          <t>MA0011</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:          - Använda och argumentera för olika metoders användning vid identifier…</t>
+          <t>Avviker från gold standard: Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.  Efter avslutad kurs skall stud…</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0011</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GMT25Z</t>
+          <t>MA0013</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:       - självständigt planera och genomföra ett maskintekniskt projektarbete in…</t>
+          <t>Avviker från gold standard: Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.  Efter avslutad kurs skall stud…</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0013</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GMT2QF</t>
+          <t>MA1040</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs skall studenten kunna:    - redogöra på principiell nivå den teoretiska grunden för finita element m…</t>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska utveckla sin förmåga att förstå och använda matematiska begrepp o…</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1040</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GMT2WL</t>
+          <t>MA1042</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs skall studenten kunna:    - skapa en CAD-modell utifrån en designidé   - redogöra för olika dataform…</t>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenterna skall tillägna sig grundläggande teoretiska kunskaper i elementär a…</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2WL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>MT1033</t>
+          <t>AMD238</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Studenten skall efter kursen kunna     - skriva ett program för styrning av en numeriskt styrd maskin som används inom v…</t>
+          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande visar sådana fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs fö…</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>MT1060</t>
+          <t>GMD2BH</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:       - redogöra för grundbegreppen spänning och töjning.    - redogöra för…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2BH</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>MT1068</t>
+          <t>GMD2EX</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:      - Identifiera kundkrav    - Specificera produktegenskaper utgående från ku…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2EX</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>MT1074</t>
+          <t>GMD2GU</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten skall tillägna sig kännedom om och förmåga till analys av de viktigas…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1074</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GU</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>MT2006</t>
+          <t>GMD2H2</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:    - göra plåtutbredning av tunnväggiga konstruktioner     - använda svetsmo…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>AEG225</t>
+          <t>GMD2H3</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna    - tillämpa och diskutera olika resultatindikatorer för att utvärdera inves…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H3</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>AEG22R</t>
+          <t>GMD2H4</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs, ska studenten kunna:       - Redogöra för grundläggande elteknik, termodynamik och mättteknik som k…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H4</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>AEG233</t>
+          <t>GMD2H5</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna       - analysera och diskutera de fysiska processer som styr utbytet av olik…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H5</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>AEG26X</t>
+          <t>GMD2HE</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgång av kursen ska studenten kunna:       - göra urval av komponenter för PV- och hybridsystem för elgenereri…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG26X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HE</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>AEG29N</t>
+          <t>GMD2HF</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kursen ska studenten kunna:    - välja ändamålsenliga komponenter för nätkopplade solcellssystem,    - red…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG29N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HF</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>AEG2B6</t>
+          <t>GMD2HG</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs skall studenten kunna:    - beskriva solljusets egenskaper före och efter passagen genom atmosfären,…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2B6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HG</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>BEG222</t>
+          <t>GMD2HH</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten skall ha nått en förtrogenhet med rådande forsknings- och utbildnings…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BEG222</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HH</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>EG1012</t>
+          <t>GMD2HJ</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenterna skall tillägna sig kunskap och förståelse för grunder i strömningsl…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG1012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HJ</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>EG2004</t>
+          <t>GMD2HK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med examensarbetet är att studenten inom givna ramar ska utföra ett arbete av utvecklingskaraktär…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HK</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>EG3007</t>
+          <t>GMD2MH</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:    - analysera och diskutera de fysikaliska processer som styr utbytet av en…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>EG3009</t>
+          <t>GMD2MJ</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:       - dimensionera en solvärmeanläggning    - designa solvärmesystem med a…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>EG3012</t>
+          <t>GMD2PA</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:        - förklara de grundläggande principerna för tekniska system vid gener…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2PA</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>GMD3FX</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:         - ange och självständigt analysera olika sätt att anpassa och design…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD3FX</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>EG3015</t>
+          <t>GMD3GZ</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs skall studenten kunna         - visa på kunskap om solljusets egenskaper före och efter passagen…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD3GZ</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>EG3017</t>
+          <t>MD1085</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs, ska studenten kunna:       - redogöra för det aktuella företagets organisation och verksamhet    -…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>EG3018</t>
+          <t>MD1097</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs, ska studenten kunna:       - redogöra för det aktuella företagets organisation och verksamhet    -…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>EG3019</t>
+          <t>MD1098</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenterna skall tillägna sig insikt i miljömässig och ekonomisk hållbarhet i…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>EG3020</t>
+          <t>MD1103</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet energitekni…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1103</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>EG3022</t>
+          <t>MD2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Målet med examensarbetet är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet solenergiteknik geno…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>EG4001</t>
+          <t>MD2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Målet med examensarbetet är att studenten ska kunna tillämpa och väsentligen fördjupa sina kunskaper inom solenergitekni…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2024</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>GEG26J</t>
+          <t>MD2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:         - Planera, skapa, och leverera tydliga vetenskapliga presentationer…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2025</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>GEG2JP</t>
+          <t>MD2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:    - redogöra för grundläggande begrepp som utgör förutsättningar för konstr…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2JP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2026</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>GEG2UE</t>
+          <t>GMT228</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Studenten skall efter genomgången kurs kunna         - kategorisera och utföra beräkningar på energianvändning i byggnad…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>GEG2UL</t>
+          <t>GMT25Z</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Den studerande ska efter avslutad kurs kunna:     - redogöra för koncept och teknologier för elkraftgenerering med utgån…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>GEG33B</t>
+          <t>GMT2QF</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Studenterna ska efter avslutad kurs kunna:    - utföra en solcellsinstallation i enlighet med gällande svenskt regelverk…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG33B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>GEG39Z</t>
+          <t>GMT2WL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs skall studenten kunna:    - beskriva skillnader mellan konventionell och omriktaransluten kraftproduk…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG39Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2WL</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>GEG3FY</t>
+          <t>GMT338</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs, ska studenten kunna:    - redogöra för den aktuella organisationens verksamhet och struktur    - gen…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3FY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT338</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>GSQ23J</t>
+          <t>GMT343</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten skall tillämpa och fördjupa kunskaper och tekniker i databashantering…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT343</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>GSQ23K</t>
+          <t>GMT344</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:       - Redogöra för fördjupade planeringteoretiska och diskursiva perspekti…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT344</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GSQ25F</t>
+          <t>GMT349</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att introducera form och gestaltning av byggnader och stadsmiljöer med fokus på verktyg för…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT349</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>GSQ25J</t>
+          <t>GMT34A</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34A</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>GSQ25K</t>
+          <t>GMT34K</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:       - Utföra stadsanalyser med stöd av GIS-verktyg    - Redogöra för och k…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34K</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>GSQ25N</t>
+          <t>GMT34L</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Examensarbetets övergripande mål är att studenten ska tillämpa och fördjupa tidigare inhämtade kunskaper och färdigheter…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34L</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>GSQ2DH</t>
+          <t>GMT34Q</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:       - Skapa tematiska kartor med hjälp av GIS    - Redogöra för projektion…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2DH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34Q</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>GSQ2H7</t>
+          <t>GMT34R</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursen syftar till att öka förståelsen för den gestaltade livsmiljöns betydelse för ett gott vardagsliv och hur den hant…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2H7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>GSQ2J4</t>
+          <t>GMT34W</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna: ·       - Redogöra för grundläggande begrepp och teorier inom såväl ekonomis…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2J4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34W</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>GSQ2L8</t>
+          <t>GMT3HZ</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:      - Redogöra för den svenska översiktliga fysiska planeringen och dess be…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3HZ</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GSQ2L9</t>
+          <t>GMT3J2</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:    - Redogöra för grundläggande geografisk informationsteknik med avseende p…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3J2</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GSQ2LA</t>
+          <t>GMT3J3</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska tillägna sig kunskap om IT och digitaliseringens betydelse och användning…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2LA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3J3</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GSQ2MC</t>
+          <t>GMT3J4</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:      - redogöra för grundläggande begrepp inom transportsektorn relevanta fö…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2MC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3J4</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GSQ2PH</t>
+          <t>GMT3JQ</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska tillägna sig fördjupade kunskaper inom fysisk planering med tyngd…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2PH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JQ</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>GSQ2R5</t>
+          <t>GMT3JR</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska skaffa sig färdigheter inom kvantitativa analyser av urbana och r…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2R5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JR</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>GSQ2VY</t>
+          <t>GMT3JT</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:    - Redogöra för begrepp inom befolkningsgeografi, demografi och social geogra…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2VY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JT</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>GSQ2WM</t>
+          <t>GMT3JU</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:       - Redogöra för grundläggande geografisk informationsteknik med avseend…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2WM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JU</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GSQ2Y2</t>
+          <t>GMT3JV</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskaplig metod. Efter genomgånge…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2Y2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JV</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>GSQ33N</t>
+          <t>GMT3JY</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:       - Utföra stadsanalyser med stöd av GIS-verktyg    - Redogöra för och k…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JY</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>SQ1003</t>
+          <t>GMT3JZ</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SQ1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JZ</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>GST2CL</t>
+          <t>MT1033</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter kursen skall studenten kunna:         - Sammanfatta och tolka data med hjälp av beskrivande statistik.    - Tolka…</t>
+          <t>Avviker från gold standard: Studenten skall efter kursen kunna…</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GST2CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1033</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>ST1013</t>
+          <t>MT1060</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter kursen skall studenten kunna:       - sammanfatta och tolka data med beskrivande statistik.    - tolka datautskrif…</t>
+          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ST1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>AMI22T</t>
+          <t>MT1068</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:       - Välja rätt statistiska modeller och metoder för dataanalys av praktiska…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1068</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>AMI22Z</t>
+          <t>MT1074</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande syftet med kursen är att studenten skall utveckla kunskap om riskhändelser och -processer med målet att…</t>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten skall tillägna sig kännedom om och förmåga till analys av de viktigas…</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1074</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>AMI23A</t>
+          <t>MT2006</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna       - visa förståelse för visual literacy, bestämma de grafiska elementen som…</t>
+          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>AMI23C</t>
+          <t>AEG225</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs skall studenten kunna:       - uttrycka praktiska problem som ett linjärprogrammeringsproblem,    -…</t>
+          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>AMI23G</t>
+          <t>AEG22R</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kursen ska studenten kunna:    - Tillämpa neurala nätverk på verklig problemlösning.   - Göra jämförande…</t>
+          <t>Avviker från gold standard: Efter avslutad kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>AMI23J</t>
+          <t>AEG233</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ges möjlighet att i en professionell miljö tillämpa sina kunskaper oc…</t>
+          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>AMI23K</t>
+          <t>AEG26X</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna       -  Redogöra för och visa förståelse för vikten av olika typer av data och…</t>
+          <t>Avviker från gold standard: Efter genomgång av kursen ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG26X</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>AMI23L</t>
+          <t>AEG294</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs kommer studenten att kunna:      - Manipulera rumslig data i både R och GIS   - Använda programvaran…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG294</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>AMI27V</t>
+          <t>AEG29N</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Avviker från gold standard</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten skall utveckla förståelse för vad som förhindrar rationellt och datad…</t>
+          <t>Avviker från gold standard: Efter godkänd kursen ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI27V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG29N</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>AMI295</t>
+          <t>AEG2AK</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska tillägna sig kunskaper om begrepp och metoder av Business Intelligence (BI…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI295</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AK</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>GMI23G</t>
+          <t>AEG2AL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:         - redogöra för olika algebraiska system, modulär aritmetik och polynom…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AL</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>GMI24H</t>
+          <t>AEG2AP</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       - Använda olika typer av datastrukturer samt visa förståelse för der…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI24H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AP</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>GMI26H</t>
+          <t>AEG2AQ</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:       - Förklara kryptografiska begrepp    - Jämföra symmetriska och asymmetris…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI26H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AQ</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>GMI2C8</t>
+          <t>AEG2AR</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Examensarbetet är det avslutande tillfället för studenten att tillämpa grundläggande kunskaper och ytterligare fördjupa…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AR</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>GMI2J3</t>
+          <t>AEG2AS</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna       - beskriva mjukvarutestningens roll i systemutvecklingsprocessen.…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2J3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AS</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>GMI2MD</t>
+          <t>AEG2AT</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad utbildning ska den studerande kunna:      Kunskap och Förståelse      - Förklara innebörden av IoT- (Inte…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2MD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AT</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>GMI2NW</t>
+          <t>AEG2AU</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska behandla aktiviteter relaterade till automatiska programvarutest…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2NW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AU</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>MI4001</t>
+          <t>AEG2AV</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar tom rad före punktlista</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna      - Analysera styrkor och begränsningar hos verktyg och tekniker som kan anvä…</t>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AV</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
+          <t>AEG2AW</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AW</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>AEG2AX</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AX</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>AEG2AY</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AY</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>AEG2B5</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2B5</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>AEG2B6</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter godkänd kurs skall studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2B6</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>AEG2C4</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2C4</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>AEG2C5</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2C5</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>BEG222</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten skall ha nått en förtrogenhet med rådande forsknings- och utbildnings…</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BEG222</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>EG1012</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenterna skall tillägna sig kunskap och förståelse för grunder i strömningsl…</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG1012</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>EG2004</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Det övergripande målet med examensarbetet är att studenten inom givna ramar ska utföra ett arbete av utvecklingskaraktär…</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>EG3007</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>EG3009</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>EG3012</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>EG3014</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>EG3015</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter genomgången kurs skall studenten kunna…</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>EG3017</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs, ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>EG3018</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs, ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>EG3019</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenterna skall tillägna sig insikt i miljömässig och ekonomisk hållbarhet i …</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3019</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>EG3020</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet energitekni…</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>EG3022</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Målet med examensarbetet är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet solenergiteknik geno…</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>EG4001</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Målet med examensarbetet är att studenten ska kunna tillämpa och väsentligen fördjupa sina kunskaper inom solenergitekni…</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>GEG26J</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>GEG2JP</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2JP</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>GEG2UE</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Studenten skall efter genomgången kurs kunna…</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UE</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>GEG2UL</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Den studerande ska efter avslutad kurs kunna:…</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UL</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>GEG2ZQ</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>GEG2ZR</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZR</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>GEG33A</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG33A</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>GEG33B</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Studenterna ska efter avslutad kurs kunna:…</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG33B</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>GEG38F</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG38F</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>GEG39Y</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG39Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>GEG39Z</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter godkänd kurs skall studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>GEG3A2</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>GEG3BX</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3BX</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>GEG3DT</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>GEG3DU</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3DU</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>GEG3DV</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3DV</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>GEG3FM</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3FM</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>GEG3FY</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter godkänd kurs, ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3FY</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>GSQ23J</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten skall tillämpa och fördjupa kunskaper och tekniker i databashantering…</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>GSQ23K</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>GSQ25F</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att introducera form och gestaltning av byggnader och stadsmiljöer med fokus på verktyg för …</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25F</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>GSQ25J</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25J</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>GSQ25K</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>GSQ25N</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Examensarbetets övergripande mål är att studenten ska tillämpa och fördjupa tidigare inhämtade kunskaper och färdigheter…</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25N</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2DH</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2DH</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2H7</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursen syftar till att öka förståelsen för den gestaltade livsmiljöns betydelse för ett gott vardagsliv och hur den hant…</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2H7</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2J4</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna: ·…</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2J4</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2L8</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2L9</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2LA</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att studenten ska tillägna sig kunskap om IT och digitaliseringens betydelse och användning …</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2LA</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2MC</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2MC</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2PH</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska tillägna sig fördjupade kunskaper inom fysisk planering med tyngd…</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2PH</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2R5</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska skaffa sig färdigheter inom kvantitativa analyser av urbana och r…</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2R5</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2VY</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2VY</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2WM</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2WM</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2Y2</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskaplig metod. Efter genomgånge…</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2Y2</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>GSQ33M</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33M</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>GSQ33N</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>SQ1003</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SQ1003</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>GST2CL</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>STA</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter kursen skall studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GST2CL</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>ST1013</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>STA</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter kursen skall studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ST1013</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>AMI22T</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22T</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>AMI22Z</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Det övergripande syftet med kursen är att studenten skall utveckla kunskap om riskhändelser och -processer med målet att…</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>AMI23A</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna…</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>AMI23C</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs skall studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23C</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>AMI23G</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kursen ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23G</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>AMI23J</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ges möjlighet att i en professionell miljö tillämpa sina kunskaper oc…</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23J</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>AMI23K</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna…</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23K</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>AMI23L</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs kommer studenten att kunna:…</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23L</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>AMI27V</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten skall utveckla förståelse för vad som förhindrar rationellt och datad…</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI27V</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>AMI295</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Kursens övergripande mål är att studenten ska tillägna sig kunskaper om begrepp och metoder av Business Intelligence (BI…</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI295</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>GMI23G</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>GMI24H</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI24H</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>GMI26H</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI26H</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>GMI2C8</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Examensarbetet är det avslutande tillfället för studenten att tillämpa grundläggande kunskaper och ytterligare fördjupa …</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>GMI2J3</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna…</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2J3</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>GMI2MD</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad utbildning ska den studerande kunna:      Kunskap och Förståelse…</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2MD</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>GMI2NW</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska behandla aktiviteter relaterade till automatiska programvarutest …</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2NW</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>GMI35R</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI35R</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>GMI35S</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Saknar tom rad före punktlista</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Saknar tom rad mellan introfras och lärandemål</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI35S</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>MI4001</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna…</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
           <t>MI4002</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="B288" t="inlineStr">
         <is>
           <t>XYZ</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Avvikande formulering</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna         - Analysera styrkor och begränsningar hos verktyg och tekniker som kan a…</t>
-        </is>
-      </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna…</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4002</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E206"/>
+  <autoFilter ref="A1:E288"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -6417,6 +8631,170 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId408"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A206" r:id="rId409"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A207" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A208" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A209" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A210" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A211" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A212" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A213" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A214" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A215" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A216" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A217" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A218" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A219" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A220" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A221" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A222" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A223" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A224" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A225" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A226" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A227" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A228" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A229" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A230" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A231" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E231" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A232" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A233" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A234" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A235" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A236" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A237" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A238" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A239" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A240" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A241" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A242" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A243" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A244" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A245" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A246" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A247" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A248" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A249" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E249" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A250" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A251" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E251" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A252" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A253" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A254" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E254" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A255" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E255" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A256" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E256" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A257" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E257" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A258" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E258" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A259" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E259" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A260" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E260" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A261" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E261" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A262" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E262" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A263" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E263" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A264" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E264" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A265" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E265" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A266" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E266" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A267" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E267" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A268" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E268" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A269" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E269" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A270" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E270" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A271" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E271" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A272" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E272" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A273" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E273" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A274" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E274" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A275" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E275" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A276" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E276" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A277" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E277" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A278" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E278" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A279" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E279" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A280" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E280" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A281" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E281" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A282" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E282" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A283" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E283" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A284" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E284" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A285" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E285" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A286" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E286" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A287" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E287" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A288" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E288" r:id="rId574"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$288</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$207</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E288"/>
+  <dimension ref="A1:E207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -482,12 +482,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -509,12 +509,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -536,12 +536,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter genomgången kurs ska studenterna kunna:…</t>
+          <t>Efter genomgången kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter godkänd kurs ska studenterna kunna:…</t>
+          <t>Efter godkänd kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -590,12 +590,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -617,12 +617,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska skaffa sig kunskaper inom samhällsplanering, byggandets regelverk…</t>
+          <t>Det övergripande målet med kursen är att studenten ska skaffa sig kunskaper inom samhällsplanering, byggandets regelverk…</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -671,12 +671,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper inom värme- och fukttransport, ljudisoleri…</t>
+          <t>Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper inom värme- och fukttransport, ljudisoleri…</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten efter genomgången kurs ska kunna rita en 3D-husmodell.      Efter gen…</t>
+          <t>Det övergripande målet med kursen är att studenten efter genomgången kurs ska kunna rita en 3D-husmodell.      Efter gen…</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -725,12 +725,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten skall skaffa sig kunskaper om såväl teoretisk som praktisk träbyggnad…</t>
+          <t>Det övergripande målet med kursen är att studenten skall skaffa sig kunskaper om såväl teoretisk som praktisk träbyggnad…</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet me kursen är att studenten ska skaffa sig kunskaper och färdigheter om systemuppbyggnad och funkt…</t>
+          <t>Det övergripande målet me kursen är att studenten ska skaffa sig kunskaper och färdigheter om systemuppbyggnad och funkt…</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -779,12 +779,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att kursdeltagaren ska skaffa sig grundläggande kunskaper om BIM (Byggnadsinformati…</t>
+          <t>Det övergripande målet med kursen är att kursdeltagaren ska skaffa sig grundläggande kunskaper om BIM (Byggnadsinformati…</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -806,12 +806,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet med examensarbetet är att studenten inom givna ramar ska utföra ett arbete av utvecklingskaraktär…</t>
+          <t>Det övergripande målet med examensarbetet är att studenten inom givna ramar ska utföra ett arbete av utvecklingskaraktär…</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska uppnå förmåga att med helhetssyn självständigt och kreativt ident…</t>
+          <t>Det övergripande målet med kursen är att studenten ska uppnå förmåga att med helhetssyn självständigt och kreativt ident…</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse_  Efter avslutad kurs ska studenten kunna:…</t>
+          <t>_Kunskap och förståelse_  Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -887,12 +887,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Vid design av energieffektiva byggnader med hög nivå av komfort och hållbarhet krävs både en djup kunskap om detaljer so…</t>
+          <t>Vid design av energieffektiva byggnader med hög nivå av komfort och hållbarhet krävs både en djup kunskap om detaljer so…</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursen fokuserar på miljöklassningsverktyg för byggnader. Efter avslutad kurs ska studenterna kunna:…</t>
+          <t>Kursen fokuserar på miljöklassningsverktyg för byggnader. Efter avslutad kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -941,12 +941,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska studenterna kunna:…</t>
+          <t>Efter avslutad kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten efter genomgången kurs ska kunna rita en 3D-modell.      Efter genomg…</t>
+          <t>Det övergripande målet med kursen är att studenten efter genomgången kurs ska kunna rita en 3D-modell.      Efter genomg…</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -995,12 +995,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska skaffa sig grundläggande kunskaper om BIM (Byggnadsinformationsmo…</t>
+          <t>Det övergripande målet med kursen är att studenten ska skaffa sig grundläggande kunskaper om BIM (Byggnadsinformationsmo…</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska skaffa sig grundläggande kunskaper inom fysisk planering med tyng…</t>
+          <t>Det övergripande målet med kursen är att studenten ska skaffa sig grundläggande kunskaper inom fysisk planering med tyng…</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att studenten ska skaffa sig kunskaper i husbyggnad, speciellt beträffande planering, utform…</t>
+          <t>Kursens övergripande mål är att studenten ska skaffa sig kunskaper i husbyggnad, speciellt beträffande planering, utform…</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper om laster och krafter i byggkonstruktioner…</t>
+          <t>Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper om laster och krafter i byggkonstruktioner…</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper för att kunna organisera och genomföra pro…</t>
+          <t>Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper för att kunna organisera och genomföra pro…</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper i husbyggnadsteknik, speciellt beträffande…</t>
+          <t>Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper i husbyggnadsteknik, speciellt beträffande…</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet är att studenten skall tillägna sig kunskaper om laster och krafter i byggkonstruktioner samt gru…</t>
+          <t>Det övergripande målet är att studenten skall tillägna sig kunskaper om laster och krafter i byggkonstruktioner samt gru…</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper om byggandets organisation och genomförand…</t>
+          <t>Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper om byggandets organisation och genomförand…</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att studenten ska tillägna sig kunskap och förståelse om fastighetsföretagens förutsättninga…</t>
+          <t>Kursens övergripande mål är att studenten ska tillägna sig kunskap och förståelse om fastighetsföretagens förutsättninga…</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten skall tillägna sig grundläggande kunskaper i arbetsplatsens organisat…</t>
+          <t>Det övergripande målet med kursen är att studenten skall tillägna sig grundläggande kunskaper i arbetsplatsens organisat…</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att öka medvetenheten om de hållbarhetsutmaningar som vi står inför. Kursen avser a…</t>
+          <t>Det övergripande målet med kursen är att öka medvetenheten om de hållbarhetsutmaningar som vi står inför. Kursen avser a…</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1373,12 +1373,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska skaffa sig kunskaper i husbyggnadsteknik, speciellt beträffande u…</t>
+          <t>Det övergripande målet med kursen är att studenten ska skaffa sig kunskaper i husbyggnadsteknik, speciellt beträffande u…</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GBY342</t>
+          <t>GBY34M</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1427,24 +1427,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter godkänd kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY342</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34M</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GBY34B</t>
+          <t>GBY34N</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1454,24 +1454,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34N</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GBY34M</t>
+          <t>GBY38D</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1481,24 +1481,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter godkänd kurs skall den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY38D</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GBY34N</t>
+          <t>GBY3AX</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1508,1050 +1508,1050 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter godkänd kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande för ett konkret husbyggnadsprojekt kunna:…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY3AX</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GBY36S</t>
+          <t>GDT2JM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BYA</t>
+          <t>DTA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY36S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JM</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GBY37D</t>
+          <t>GDT2JN</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BYA</t>
+          <t>DTA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY37D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JN</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GBY38D</t>
+          <t>GDT34Z</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BYA</t>
+          <t>DTA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter godkänd kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY38D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT34Z</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GBY38E</t>
+          <t>ET1029</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BYA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY38E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ET1029</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GBY3AX</t>
+          <t>BFY224</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BYA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande för ett konkret husbyggnadsprojekt kunna:…</t>
+          <t>Kursens övergripande mål är att den studerande ska tillägna sig kunskap om vetenskapligt arbetssätt inom naturvetenskap …</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY3AX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY224</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GBY3DW</t>
+          <t>FY1018</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BYA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Studenten skall efter genomgången kurs kunna…</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY3DW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FY1018</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GBY3DX</t>
+          <t>GIE26L</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BYA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>_Kunskap och förståelse_   Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY3DX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26L</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GDT2JM</t>
+          <t>GIE26M</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DTA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs skall studenten kunna:…</t>
+          <t>_Kunskap och förståelse_   Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26M</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GDT2JN</t>
+          <t>GIE26N</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DTA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs skall studenten kunna:…</t>
+          <t>_Kunskap och förståelse_   Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26N</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GDT34Z</t>
+          <t>GIE26P</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DTA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter godkänd kurs skall studenten kunna:…</t>
+          <t>_Kunskap och förståelse    _Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT34Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26P</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GDT3CR</t>
+          <t>GIE29N</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DTA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>_Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT3CR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE29N</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>ET1029</t>
+          <t>GIE2L7</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>_Kunskap och förståelse    _Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ET1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2L7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GET36T</t>
+          <t>GIE2MF</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>_Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GET36T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2MF</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>BFY224</t>
+          <t>GIE2QS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska tillägna sig kunskap om vetenskapligt arbetssätt inom naturvetenskap …</t>
+          <t>**Kunskap och förståelse**  Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY224</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2QS</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>BFY225</t>
+          <t>GIE2RF</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>_Kunskap och förståelse_      Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY225</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2RF</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>BFY226</t>
+          <t>IE1068</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>_Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY226</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1068</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>BFY227</t>
+          <t>IE1069</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>_Kunskap och förståelse_   Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1069</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>FY1018</t>
+          <t>IE1076</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Studenten skall efter genomgången kurs kunna…</t>
+          <t>_Kunskap och förståelse    _Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FY1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1076</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GFY345</t>
+          <t>IE2003</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>De allmänna målen med examensarbetet är att ge kursdeltagarna möjligheter att utveckla sin förmåga att inom ämnet indust…</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFY345</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE2003</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GIE26L</t>
+          <t>AIK232</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse_   Efter avslutad kurs ska studenten kunna:…</t>
+          <t>_Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GIE26M</t>
+          <t>GIK23M</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse_   Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda …</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK23M</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GIE26N</t>
+          <t>GIK289</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse_   Efter avslutad kurs ska studenten kunna:…</t>
+          <t>_Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK289</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GIE26P</t>
+          <t>GIK28T</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse    _Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna      _Kunskap och förståelse_…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GIE29N</t>
+          <t>GIK299</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna…</t>
+          <t>Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper och färdigheter i att utveckla prog…</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE29N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK299</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GIE2L7</t>
+          <t>GIK29B</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse    _Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2L7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK29B</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GIE2MF</t>
+          <t>GIK2AL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda …</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2MF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2AL</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GIE2QS</t>
+          <t>GIK2BD</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: **Kunskap och förståelse**  Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Kunskap och förståelse    Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2QS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2BD</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GIE2RF</t>
+          <t>GIK2FB</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse_      Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Kunskap och förståelse  Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2RF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2FB</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GIE36Y</t>
+          <t>GIK2JX</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>**Kunskap och förståelse   **Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE36Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2JX</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GIE36Z</t>
+          <t>GIK2KM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att använda och utveckla mju…</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE36Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2KM</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GIE372</t>
+          <t>GIK2LF</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>_Kunskap och förståelse   _Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE372</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2LF</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GIE3FW</t>
+          <t>GIK2NV</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att hantera data över ett da…</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3FW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NV</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GIE3H2</t>
+          <t>GIK2NX</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att den studerande tillägnar sig kunskaper och färdigheter i att samla in och bearbeta data …</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3H2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NX</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GIE3JW</t>
+          <t>GIK2PB</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att den studerande ska tillägna sig kunskap om och förståelse för systemförvaltning och test…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3JW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PB</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>IE1068</t>
+          <t>GIK2PD</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Kursens övergripande mål är att introducera studenten till nätverk, nätverkstjänster , nätverkssäkerhet, datakommunikati…</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PD</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>IE1069</t>
+          <t>GIK2PF</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse_   Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Det övergripande målet är att studenterna förvärvar fördjupade kunskaper och färdigheter inom IT-arkitektur som omfattar…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PF</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>IE1076</t>
+          <t>GIK2PG</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse    _Efter avslutad kurs ska studenten kunna…</t>
+          <t>Det övergripande målet med kursen är att studenter i grupp i ett systemutvecklingsprojekt planerar, analyserar, designar…</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1076</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PG</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>IE2003</t>
+          <t>GIK2Q3</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: De allmänna målen med examensarbetet är att ge kursdeltagarna möjligheter att utveckla sin förmåga att inom ämnet indust…</t>
+          <t>Efter avslutad kurs ska studenten kunna:    _   Kunskap och förståelse_…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2Q3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>AIK232</t>
+          <t>GIK2QZ</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna:…</t>
+          <t>_Kunskap och förståelse_     Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2QZ</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GIK23M</t>
+          <t>GIK2UK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2588,24 +2588,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda …</t>
+          <t>Kunskap och förståelse   Efter genomförd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK23M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2UK</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GIK289</t>
+          <t>GIK2V4</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2615,24 +2615,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Kursens övergripande mål är att introducera studenten till cybersäkerhetstrender, hotbilder vid IT-användning mot person…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2V4</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GIK28T</t>
+          <t>GIK2XJ</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2642,24 +2642,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna      _Kunskap och förståelse_…</t>
+          <t>Kunskap och förståelse    Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XJ</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GIK299</t>
+          <t>GIK2XK</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2669,24 +2669,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper och färdigheter i att utveckla prog…</t>
+          <t>**Kunskap och förståelse**   Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK299</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XK</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GIK29B</t>
+          <t>GIK2XZ</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2696,24 +2696,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
+          <t>**Kunskap och förståelse   **Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK29B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XZ</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GIK2AL</t>
+          <t>GIK2YK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2723,24 +2723,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda …</t>
+          <t>_Kunskap och förståelse   _Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YK</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GIK2BD</t>
+          <t>GIK2YL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2750,24 +2750,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kunskap och förståelse    Efter avslutad kurs ska den studerande kunna…</t>
+          <t>_Kunskap och förståelse   _Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2BD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YL</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GIK2FB</t>
+          <t>GIK2YN</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2777,24 +2777,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kunskap och förståelse  Efter avslutad kurs ska studenten kunna:…</t>
+          <t>_Kunskap och förståelse   _Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2FB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YN</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GIK2JX</t>
+          <t>GIK2YP</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2804,24 +2804,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: **Kunskap och förståelse   **Efter avslutad kurs ska studenten kunna:…</t>
+          <t>_Kunskap och förståelse_   Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2JX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YP</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GIK2KM</t>
+          <t>GIK2YR</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2831,24 +2831,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att använda och utveckla mju…</t>
+          <t>Kunskap och förståelse   Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2KM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YR</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GIK2LF</t>
+          <t>GIK32K</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2858,24 +2858,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse   _Efter avslutad kurs ska den studerande kunna…</t>
+          <t>_Kunskap och förståelse _  Efter godkänd kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2LF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32K</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GIK2NV</t>
+          <t>GIK32L</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2885,24 +2885,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att hantera data över ett da…</t>
+          <t>_Kunskap och förståelse _  Efter godkänd kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32L</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GIK2NX</t>
+          <t>GIK32M</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2912,24 +2912,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande tillägnar sig kunskaper och färdigheter i att samla in och bearbeta data …</t>
+          <t>_Kunskap och förståelse _  Efter godkänd kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32M</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GIK2PB</t>
+          <t>GIK32N</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2939,24 +2939,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska tillägna sig kunskap om och förståelse för systemförvaltning och test…</t>
+          <t>_Kunskap och förståelse _  Efter godkänd kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32N</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GIK2PD</t>
+          <t>GIK339</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2966,24 +2966,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att introducera studenten till nätverk, nätverkstjänster , nätverkssäkerhet, datakommunikati…</t>
+          <t>_Kunskap och förståelse_   Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK339</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GIK2PF</t>
+          <t>GIK347</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2993,24 +2993,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet är att studenterna förvärvar fördjupade kunskaper och färdigheter inom IT-arkitektur som omfattar…</t>
+          <t>_Kunskap och förståelse    _Efter godkänd kurs ska den studenten kunna…</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK347</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GIK2PG</t>
+          <t>IK1032</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3020,24 +3020,24 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenter i grupp i ett systemutvecklingsprojekt planerar, analyserar, designar…</t>
+          <t>Målet med examensarbetet är att studenten ska förvärva fördjupade kunskaper inom examensarbetets ämnesområde genom att u…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1032</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GIK2Q3</t>
+          <t>IK1064</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3047,24 +3047,24 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:    _   Kunskap och förståelse_…</t>
+          <t>Kursens övergripande mål är att den studerande ska tillägna sig utökade kunskaper i objektorienterad programmering och m…</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2Q3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1064</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GIK2QZ</t>
+          <t>IK1066</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3074,5152 +3074,2965 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse_     Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Kursens övergripande mål är att den studerande tillägnar sig fördjupade kunskaper och färdigheter inom ämnesområdet geno…</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2QZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1066</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GIK2UK</t>
+          <t>GMA28W</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kunskap och förståelse   Efter genomförd kurs skall studenten kunna:…</t>
+          <t>Det övergripande målet med kursen är att studenten ska öka sin förmåga att förstå och använda grundläggande matematiska …</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2UK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA28W</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GIK2V4</t>
+          <t>GMA2EY</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att introducera studenten till cybersäkerhetstrender, hotbilder vid IT-användning mot person…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2V4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GIK2XJ</t>
+          <t>MA0011</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kunskap och förståelse    Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.  Efter avslutad kurs skall stud…</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0011</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GIK2XK</t>
+          <t>MA0013</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: **Kunskap och förståelse**   Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.  Efter avslutad kurs skall stud…</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0013</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GIK2XZ</t>
+          <t>MA1040</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: **Kunskap och förståelse   **Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Det övergripande målet med kursen är att studenten ska utveckla sin förmåga att förstå och använda matematiska begrepp o…</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1040</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GIK2YK</t>
+          <t>MA1042</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse   _Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Det övergripande målet med kursen är att studenterna skall tillägna sig grundläggande teoretiska kunskaper i elementär a…</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GIK2YL</t>
+          <t>AMD238</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse   _Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Kursens övergripande mål är att den studerande visar sådana fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs fö…</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GIK2YN</t>
+          <t>GMD2BH</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse   _Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2BH</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GIK2YP</t>
+          <t>GMD2EX</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse_   Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2EX</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GIK2YR</t>
+          <t>GMD2GU</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kunskap och förståelse   Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GU</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GIK32J</t>
+          <t>GMD2H2</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GIK32K</t>
+          <t>GMD2H3</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse _  Efter godkänd kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GIK32L</t>
+          <t>GMD2H4</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse _  Efter godkänd kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H4</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GIK32M</t>
+          <t>GMD2H5</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse _  Efter godkänd kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H5</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GIK32N</t>
+          <t>GMD2HE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse _  Efter godkänd kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HE</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GIK339</t>
+          <t>GMD2HF</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse_   Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK339</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HF</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GIK346</t>
+          <t>GMD2HG</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK346</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HG</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GIK347</t>
+          <t>GMD2HH</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: _Kunskap och förståelse    _Efter godkänd kurs ska den studenten kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK347</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HH</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GIK348</t>
+          <t>GMD2HJ</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK348</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HJ</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GIK34Y</t>
+          <t>GMD2HK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK34Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HK</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GIK373</t>
+          <t>GMD2MH</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK373</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GIK38G</t>
+          <t>GMD2MJ</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK38G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GIK38H</t>
+          <t>GMD2PA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK38H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2PA</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>IK1032</t>
+          <t>GMD3GZ</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Målet med examensarbetet är att studenten ska förvärva fördjupade kunskaper inom examensarbetets ämnesområde genom att u…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD3GZ</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>IK1064</t>
+          <t>MD1085</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande ska tillägna sig utökade kunskaper i objektorienterad programmering och m…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>IK1066</t>
+          <t>MD1097</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande tillägnar sig fördjupade kunskaper och färdigheter inom ämnesområdet geno…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GMA28W</t>
+          <t>MD1098</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska öka sin förmåga att förstå och använda grundläggande matematiska …</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA28W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GMA2EY</t>
+          <t>MD1103</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1103</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GMA2ZS</t>
+          <t>MD2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2ZS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GMA2ZT</t>
+          <t>MD2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2ZT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2024</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GMA33Z</t>
+          <t>MD2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA33Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2025</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>MA0011</t>
+          <t>MD2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.  Efter avslutad kurs skall stud…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2026</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>MA0013</t>
+          <t>GMT228</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.  Efter avslutad kurs skall stud…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>MA1040</t>
+          <t>GMT25Z</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska utveckla sin förmåga att förstå och använda matematiska begrepp o…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1040</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>MA1042</t>
+          <t>GMT2QF</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenterna skall tillägna sig grundläggande teoretiska kunskaper i elementär a…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>AMD238</t>
+          <t>GMT2WL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att den studerande visar sådana fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs fö…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2WL</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GMD2BH</t>
+          <t>MT1033</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Studenten skall efter kursen kunna…</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1033</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GMD2EX</t>
+          <t>MT1060</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2EX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GMD2GU</t>
+          <t>MT1068</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1068</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GMD2H2</t>
+          <t>MT1074</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Det övergripande målet med kursen är att studenten skall tillägna sig kännedom om och förmåga till analys av de viktigas…</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1074</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GMD2H3</t>
+          <t>MT2006</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GMD2H4</t>
+          <t>AEG225</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GMD2H5</t>
+          <t>AEG22R</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GMD2HE</t>
+          <t>AEG233</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GMD2HF</t>
+          <t>AEG26X</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgång av kursen ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG26X</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GMD2HG</t>
+          <t>AEG29N</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kursen ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG29N</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GMD2HH</t>
+          <t>AEG2B6</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2B6</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GMD2HJ</t>
+          <t>BEG222</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Det övergripande målet med kursen är att studenten skall ha nått en förtrogenhet med rådande forsknings- och utbildnings…</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BEG222</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GMD2HK</t>
+          <t>EG1012</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Det övergripande målet med kursen är att studenterna skall tillägna sig kunskap och förståelse för grunder i strömningsl…</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG1012</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GMD2MH</t>
+          <t>EG2004</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Det övergripande målet med examensarbetet är att studenten inom givna ramar ska utföra ett arbete av utvecklingskaraktär…</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG2004</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GMD2MJ</t>
+          <t>EG3007</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GMD2PA</t>
+          <t>EG3009</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2PA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GMD3FX</t>
+          <t>EG3012</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD3FX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GMD3GZ</t>
+          <t>EG3014</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD3GZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>MD1085</t>
+          <t>EG3015</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten kunna…</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>MD1097</t>
+          <t>EG3017</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>MD1098</t>
+          <t>EG3018</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>MD1103</t>
+          <t>EG3019</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Det övergripande målet med kursen är att studenterna skall tillägna sig insikt i miljömässig och ekonomisk hållbarhet i …</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1103</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3019</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>MD2023</t>
+          <t>EG3020</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Det övergripande målet med kursen är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet energitekni…</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>MD2024</t>
+          <t>EG3022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Målet med examensarbetet är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet solenergiteknik geno…</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>MD2025</t>
+          <t>EG4001</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Målet med examensarbetet är att studenten ska kunna tillämpa och väsentligen fördjupa sina kunskaper inom solenergitekni…</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>MD2026</t>
+          <t>GEG26J</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>GMT228</t>
+          <t>GEG2JP</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2JP</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>GMT25Z</t>
+          <t>GEG2UE</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Studenten skall efter genomgången kurs kunna…</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UE</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>GMT2QF</t>
+          <t>GEG2UL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Den studerande ska efter avslutad kurs kunna:…</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UL</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>GMT2WL</t>
+          <t>GEG33B</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Studenterna ska efter avslutad kurs kunna:…</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2WL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG33B</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>GMT338</t>
+          <t>GEG39Z</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT338</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG39Z</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>GMT343</t>
+          <t>GEG3FY</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter godkänd kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT343</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3FY</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>GMT344</t>
+          <t>GSQ23J</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Det övergripande målet med kursen är att studenten skall tillämpa och fördjupa kunskaper och tekniker i databashantering…</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT344</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GMT349</t>
+          <t>GSQ23K</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT349</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>GMT34A</t>
+          <t>GSQ25F</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att introducera form och gestaltning av byggnader och stadsmiljöer med fokus på verktyg för …</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25F</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>GMT34K</t>
+          <t>GSQ25J</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25J</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>GMT34L</t>
+          <t>GSQ25K</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>GMT34Q</t>
+          <t>GSQ25N</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Examensarbetets övergripande mål är att studenten ska tillämpa och fördjupa tidigare inhämtade kunskaper och färdigheter…</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25N</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>GMT34R</t>
+          <t>GSQ2DH</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2DH</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>GMT34W</t>
+          <t>GSQ2H7</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursen syftar till att öka förståelsen för den gestaltade livsmiljöns betydelse för ett gott vardagsliv och hur den hant…</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2H7</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>GMT3HZ</t>
+          <t>GSQ2J4</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter genomgången kurs ska studenten kunna: ·…</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3HZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2J4</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GMT3J2</t>
+          <t>GSQ2L8</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3J2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L8</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GMT3J3</t>
+          <t>GSQ2L9</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3J3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L9</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GMT3J4</t>
+          <t>GSQ2LA</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att studenten ska tillägna sig kunskap om IT och digitaliseringens betydelse och användning …</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3J4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2LA</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GMT3JQ</t>
+          <t>GSQ2MC</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2MC</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>GMT3JR</t>
+          <t>GSQ2PH</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Det övergripande målet med kursen är att studenten ska tillägna sig fördjupade kunskaper inom fysisk planering med tyngd…</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2PH</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>GMT3JT</t>
+          <t>GSQ2R5</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Det övergripande målet med kursen är att studenten ska skaffa sig färdigheter inom kvantitativa analyser av urbana och r…</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2R5</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>GMT3JU</t>
+          <t>GSQ2VY</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2VY</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GMT3JV</t>
+          <t>GSQ2WM</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2WM</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>GMT3JY</t>
+          <t>GSQ2Y2</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskaplig metod. Efter genomgånge…</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2Y2</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>GMT3JZ</t>
+          <t>GSQ33N</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>MT1033</t>
+          <t>SQ1003</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Studenten skall efter kursen kunna…</t>
+          <t>Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SQ1003</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>MT1060</t>
+          <t>GST2CL</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>STA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter kursen skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GST2CL</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>MT1068</t>
+          <t>ST1013</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>STA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter kursen skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ST1013</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>MT1074</t>
+          <t>AMI22T</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten skall tillägna sig kännedom om och förmåga till analys av de viktigas…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1074</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22T</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>MT2006</t>
+          <t>AMI22Z</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Det övergripande syftet med kursen är att studenten skall utveckla kunskap om riskhändelser och -processer med målet att…</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22Z</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>AEG225</t>
+          <t>AMI23A</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>AEG22R</t>
+          <t>AMI23C</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter avslutad kurs, ska studenten kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23C</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>AEG233</t>
+          <t>AMI23G</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna…</t>
+          <t>Efter avslutad kursen ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23G</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>AEG26X</t>
+          <t>AMI23J</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter genomgång av kursen ska studenten kunna:…</t>
+          <t>Det övergripande målet med kursen är att studenten ges möjlighet att i en professionell miljö tillämpa sina kunskaper oc…</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG26X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23J</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>AEG294</t>
+          <t>AMI23K</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG294</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23K</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>AEG29N</t>
+          <t>AMI23L</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Avviker från gold standard</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Avviker från gold standard: Efter godkänd kursen ska studenten kunna:…</t>
+          <t>Efter avslutad kurs kommer studenten att kunna:…</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG29N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23L</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>AEG2AK</t>
+          <t>AMI27V</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Det övergripande målet med kursen är att studenten skall utveckla förståelse för vad som förhindrar rationellt och datad…</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI27V</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>AEG2AL</t>
+          <t>AMI295</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Kursens övergripande mål är att studenten ska tillägna sig kunskaper om begrepp och metoder av Business Intelligence (BI…</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI295</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>AEG2AP</t>
+          <t>GMI23G</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>AEG2AQ</t>
+          <t>GMI24H</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI24H</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>AEG2AR</t>
+          <t>GMI26H</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI26H</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>AEG2AS</t>
+          <t>GMI2C8</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Examensarbetet är det avslutande tillfället för studenten att tillämpa grundläggande kunskaper och ytterligare fördjupa …</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>AEG2AT</t>
+          <t>GMI2J3</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2J3</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>AEG2AU</t>
+          <t>GMI2MD</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad utbildning ska den studerande kunna:      Kunskap och Förståelse…</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2MD</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>AEG2AV</t>
+          <t>GMI2NW</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Det övergripande målet med kursen är att studenten ska behandla aktiviteter relaterade till automatiska programvarutest …</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2NW</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>AEG2AW</t>
+          <t>MI4001</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>AEG2AX</t>
+          <t>MI4002</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Saknar tom rad före punktlista</t>
+          <t>Avviker från referensformen</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AX</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
-        <is>
-          <t>AEG2AY</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E208" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AY</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
-        <is>
-          <t>AEG2B5</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E209" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2B5</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
-        <is>
-          <t>AEG2B6</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter godkänd kurs skall studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E210" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2B6</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
-        <is>
-          <t>AEG2C4</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E211" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2C4</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
-        <is>
-          <t>AEG2C5</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E212" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2C5</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
-        <is>
-          <t>BEG222</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten skall ha nått en förtrogenhet med rådande forsknings- och utbildnings…</t>
-        </is>
-      </c>
-      <c r="E213" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BEG222</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>EG1012</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenterna skall tillägna sig kunskap och förståelse för grunder i strömningsl…</t>
-        </is>
-      </c>
-      <c r="E214" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG1012</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
-        <is>
-          <t>EG2004</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Det övergripande målet med examensarbetet är att studenten inom givna ramar ska utföra ett arbete av utvecklingskaraktär…</t>
-        </is>
-      </c>
-      <c r="E215" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG2004</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
-        <is>
-          <t>EG3007</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E216" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
-        <is>
-          <t>EG3009</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E217" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
-        <is>
-          <t>EG3012</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E218" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
-        <is>
-          <t>EG3014</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E219" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
-        <is>
-          <t>EG3015</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter genomgången kurs skall studenten kunna…</t>
-        </is>
-      </c>
-      <c r="E220" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>EG3017</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs, ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E221" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>EG3018</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs, ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E222" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
-        <is>
-          <t>EG3019</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenterna skall tillägna sig insikt i miljömässig och ekonomisk hållbarhet i …</t>
-        </is>
-      </c>
-      <c r="E223" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3019</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
-        <is>
-          <t>EG3020</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet energitekni…</t>
-        </is>
-      </c>
-      <c r="E224" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
-        <is>
-          <t>EG3022</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Målet med examensarbetet är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet solenergiteknik geno…</t>
-        </is>
-      </c>
-      <c r="E225" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
-        <is>
-          <t>EG4001</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Målet med examensarbetet är att studenten ska kunna tillämpa och väsentligen fördjupa sina kunskaper inom solenergitekni…</t>
-        </is>
-      </c>
-      <c r="E226" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
-        <is>
-          <t>GEG26J</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E227" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
-        <is>
-          <t>GEG2JP</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E228" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2JP</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
-        <is>
-          <t>GEG2UE</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Studenten skall efter genomgången kurs kunna…</t>
-        </is>
-      </c>
-      <c r="E229" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UE</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
-        <is>
-          <t>GEG2UL</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Den studerande ska efter avslutad kurs kunna:…</t>
-        </is>
-      </c>
-      <c r="E230" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UL</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="2" t="inlineStr">
-        <is>
-          <t>GEG2ZQ</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E231" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="2" t="inlineStr">
-        <is>
-          <t>GEG2ZR</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E232" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZR</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="2" t="inlineStr">
-        <is>
-          <t>GEG33A</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E233" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG33A</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
-        <is>
-          <t>GEG33B</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Studenterna ska efter avslutad kurs kunna:…</t>
-        </is>
-      </c>
-      <c r="E234" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG33B</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
-        <is>
-          <t>GEG38F</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E235" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG38F</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
-        <is>
-          <t>GEG39Y</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E236" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG39Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="2" t="inlineStr">
-        <is>
-          <t>GEG39Z</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter godkänd kurs skall studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E237" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG39Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>GEG3A2</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E238" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3A2</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
-        <is>
-          <t>GEG3BX</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E239" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3BX</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
-        <is>
-          <t>GEG3DT</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E240" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3DT</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>GEG3DU</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E241" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3DU</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
-        <is>
-          <t>GEG3DV</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E242" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3DV</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="2" t="inlineStr">
-        <is>
-          <t>GEG3FM</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E243" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3FM</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="2" t="inlineStr">
-        <is>
-          <t>GEG3FY</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter godkänd kurs, ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E244" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3FY</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
-        <is>
-          <t>GSQ23J</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten skall tillämpa och fördjupa kunskaper och tekniker i databashantering…</t>
-        </is>
-      </c>
-      <c r="E245" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
-        <is>
-          <t>GSQ23K</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E246" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
-        <is>
-          <t>GSQ25F</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att introducera form och gestaltning av byggnader och stadsmiljöer med fokus på verktyg för …</t>
-        </is>
-      </c>
-      <c r="E247" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25F</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>GSQ25J</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
-        </is>
-      </c>
-      <c r="E248" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25J</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
-        <is>
-          <t>GSQ25K</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E249" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
-        <is>
-          <t>GSQ25N</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Examensarbetets övergripande mål är att studenten ska tillämpa och fördjupa tidigare inhämtade kunskaper och färdigheter…</t>
-        </is>
-      </c>
-      <c r="E250" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25N</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2DH</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E251" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2DH</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2H7</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursen syftar till att öka förståelsen för den gestaltade livsmiljöns betydelse för ett gott vardagsliv och hur den hant…</t>
-        </is>
-      </c>
-      <c r="E252" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2H7</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2J4</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna: ·…</t>
-        </is>
-      </c>
-      <c r="E253" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2J4</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2L8</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E254" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L8</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2L9</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E255" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L9</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2LA</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att studenten ska tillägna sig kunskap om IT och digitaliseringens betydelse och användning …</t>
-        </is>
-      </c>
-      <c r="E256" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2LA</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2MC</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E257" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2MC</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2PH</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska tillägna sig fördjupade kunskaper inom fysisk planering med tyngd…</t>
-        </is>
-      </c>
-      <c r="E258" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2PH</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2R5</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska skaffa sig färdigheter inom kvantitativa analyser av urbana och r…</t>
-        </is>
-      </c>
-      <c r="E259" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2R5</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2VY</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E260" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2VY</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2WM</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E261" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2WM</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2Y2</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskaplig metod. Efter genomgånge…</t>
-        </is>
-      </c>
-      <c r="E262" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2Y2</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="2" t="inlineStr">
-        <is>
-          <t>GSQ33M</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E263" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33M</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="2" t="inlineStr">
-        <is>
-          <t>GSQ33N</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter genomgången kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E264" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="2" t="inlineStr">
-        <is>
-          <t>SQ1003</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
-        </is>
-      </c>
-      <c r="E265" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SQ1003</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="2" t="inlineStr">
-        <is>
-          <t>GST2CL</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>STA</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter kursen skall studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E266" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GST2CL</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="2" t="inlineStr">
-        <is>
-          <t>ST1013</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>STA</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter kursen skall studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E267" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ST1013</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="2" t="inlineStr">
-        <is>
-          <t>AMI22T</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E268" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22T</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="2" t="inlineStr">
-        <is>
-          <t>AMI22Z</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Det övergripande syftet med kursen är att studenten skall utveckla kunskap om riskhändelser och -processer med målet att…</t>
-        </is>
-      </c>
-      <c r="E269" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="2" t="inlineStr">
-        <is>
-          <t>AMI23A</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna…</t>
-        </is>
-      </c>
-      <c r="E270" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="2" t="inlineStr">
-        <is>
-          <t>AMI23C</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs skall studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E271" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23C</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="2" t="inlineStr">
-        <is>
-          <t>AMI23G</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kursen ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E272" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23G</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="2" t="inlineStr">
-        <is>
-          <t>AMI23J</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ges möjlighet att i en professionell miljö tillämpa sina kunskaper oc…</t>
-        </is>
-      </c>
-      <c r="E273" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23J</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="2" t="inlineStr">
-        <is>
-          <t>AMI23K</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna…</t>
-        </is>
-      </c>
-      <c r="E274" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23K</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="2" t="inlineStr">
-        <is>
-          <t>AMI23L</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs kommer studenten att kunna:…</t>
-        </is>
-      </c>
-      <c r="E275" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23L</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="2" t="inlineStr">
-        <is>
-          <t>AMI27V</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten skall utveckla förståelse för vad som förhindrar rationellt och datad…</t>
-        </is>
-      </c>
-      <c r="E276" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI27V</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="2" t="inlineStr">
-        <is>
-          <t>AMI295</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Kursens övergripande mål är att studenten ska tillägna sig kunskaper om begrepp och metoder av Business Intelligence (BI…</t>
-        </is>
-      </c>
-      <c r="E277" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI295</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="2" t="inlineStr">
-        <is>
-          <t>GMI23G</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E278" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="2" t="inlineStr">
-        <is>
-          <t>GMI24H</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E279" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI24H</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="2" t="inlineStr">
-        <is>
-          <t>GMI26H</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E280" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI26H</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="2" t="inlineStr">
-        <is>
-          <t>GMI2C8</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Examensarbetet är det avslutande tillfället för studenten att tillämpa grundläggande kunskaper och ytterligare fördjupa …</t>
-        </is>
-      </c>
-      <c r="E281" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="2" t="inlineStr">
-        <is>
-          <t>GMI2J3</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska den studerande kunna…</t>
-        </is>
-      </c>
-      <c r="E282" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2J3</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="2" t="inlineStr">
-        <is>
-          <t>GMI2MD</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad utbildning ska den studerande kunna:      Kunskap och Förståelse…</t>
-        </is>
-      </c>
-      <c r="E283" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2MD</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="2" t="inlineStr">
-        <is>
-          <t>GMI2NW</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Det övergripande målet med kursen är att studenten ska behandla aktiviteter relaterade till automatiska programvarutest …</t>
-        </is>
-      </c>
-      <c r="E284" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2NW</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="2" t="inlineStr">
-        <is>
-          <t>GMI35R</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E285" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI35R</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="2" t="inlineStr">
-        <is>
-          <t>GMI35S</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>Saknar tom rad före punktlista</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>Saknar tom rad mellan introfras och lärandemål</t>
-        </is>
-      </c>
-      <c r="E286" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI35S</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="2" t="inlineStr">
-        <is>
-          <t>MI4001</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna…</t>
-        </is>
-      </c>
-      <c r="E287" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="2" t="inlineStr">
-        <is>
-          <t>MI4002</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>Avviker från gold standard: Efter avslutad kurs ska studenten kunna…</t>
-        </is>
-      </c>
-      <c r="E288" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4002</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E288"/>
+  <autoFilter ref="A1:E207"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -8633,168 +6446,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId410"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A207" r:id="rId411"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A208" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A209" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A210" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A211" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A212" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A213" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A214" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A215" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A216" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A217" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A218" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A219" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A220" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A221" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A222" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A223" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A224" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A225" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A226" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A227" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A228" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A229" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A230" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A231" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E231" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A232" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A233" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A234" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A235" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A236" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A237" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A238" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A239" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A240" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A241" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A242" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A243" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A244" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A245" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A246" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A247" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A248" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A249" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E249" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A250" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A251" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E251" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A252" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A253" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A254" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E254" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A255" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E255" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A256" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E256" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A257" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E257" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A258" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E258" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A259" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E259" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A260" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E260" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A261" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E261" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A262" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E262" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A263" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E263" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A264" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E264" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A265" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E265" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A266" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E266" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A267" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E267" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A268" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E268" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A269" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E269" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A270" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E270" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A271" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E271" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A272" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E272" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A273" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E273" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A274" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E274" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A275" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E275" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A276" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E276" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A277" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E277" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A278" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E278" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A279" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E279" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A280" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E280" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A281" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E281" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A282" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E282" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A283" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E283" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A284" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E284" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A285" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E285" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A286" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E286" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A287" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E287" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A288" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E288" r:id="rId574"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$119</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -634,7 +634,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>BY3005</t>
+          <t>BY2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenterna kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY2025</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GBY2RN</t>
+          <t>BY3005</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -676,19 +676,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2RN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY3005</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GBY2V5</t>
+          <t>GBY2RN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2V5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2RN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GBY2V8</t>
+          <t>GBY2V5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -730,19 +730,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2V8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2V5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GBY33L</t>
+          <t>GBY2V8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -762,14 +762,14 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY33L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2V8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GBY34M</t>
+          <t>GBY33L</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -784,19 +784,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs skall den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY33L</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GBY34N</t>
+          <t>GBY34M</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs skall studenten kunna:…</t>
+          <t>Efter godkänd kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34M</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GBY38D</t>
+          <t>GBY34N</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -838,19 +838,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY38D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34N</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GBY3AX</t>
+          <t>GBY38D</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande för ett konkret husbyggnadsprojekt kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY3AX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY38D</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GDT2JM</t>
+          <t>GBY3AX</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DTA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -892,19 +892,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande för ett konkret husbyggnadsprojekt kunna:…</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY3AX</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GDT2JN</t>
+          <t>GDT2JM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -924,14 +924,14 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JM</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GDT34Z</t>
+          <t>GDT2JN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT34Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ET1029</t>
+          <t>GDT34Z</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>DTA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ET1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT34Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GIE36Z</t>
+          <t>ET1029</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna:_…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE36Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ET1029</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GIK28T</t>
+          <t>GIE26L</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26L</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GIK29B</t>
+          <t>GIE26M</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK29B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26M</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GIK2Q3</t>
+          <t>GIE26N</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1086,19 +1086,19 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2Q3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26N</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GMA2EY</t>
+          <t>GIE2QS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1113,19 +1113,19 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2QS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GMD2BH</t>
+          <t>GIE2RF</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2RF</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GMD2EX</t>
+          <t>GIE36Z</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna:_…</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2EX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE36Z</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GMD2GU</t>
+          <t>IE1069</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1069</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GMD2H2</t>
+          <t>GIK28T</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GMD2H3</t>
+          <t>GIK29B</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK29B</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GMD2H4</t>
+          <t>GIK2BD</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2BD</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GMD2H5</t>
+          <t>GIK2FB</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2FB</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GMD2HE</t>
+          <t>GIK2Q3</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2Q3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GMD2HF</t>
+          <t>GIK2QZ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2QZ</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GMD2HG</t>
+          <t>GIK2UK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomförd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2UK</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GMD2HH</t>
+          <t>GIK2XJ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XJ</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GMD2HJ</t>
+          <t>GIK2XK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1437,19 +1437,19 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XK</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GMD2HK</t>
+          <t>GIK2YP</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YP</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GMD2MH</t>
+          <t>GIK2YR</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YR</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GMD2MJ</t>
+          <t>GIK32K</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32K</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GMD2PA</t>
+          <t>GIK32L</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande…</t>
+          <t>Efter godkänd kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2PA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32L</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GMD3GZ</t>
+          <t>GIK32M</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD3GZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32M</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>MD1085</t>
+          <t>GIK32N</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32N</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>MD1097</t>
+          <t>GIK339</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK339</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>MD1098</t>
+          <t>GMA2EY</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1648,19 +1648,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>MD1103</t>
+          <t>GMD2BH</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1680,14 +1680,14 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1103</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2BH</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>MD2023</t>
+          <t>GMD2EX</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1707,14 +1707,14 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2EX</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>MD2024</t>
+          <t>GMD2GU</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1734,14 +1734,14 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GU</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>MD2025</t>
+          <t>GMD2H2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1761,14 +1761,14 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>MD2026</t>
+          <t>GMD2H3</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1788,19 +1788,19 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GMT228</t>
+          <t>GMD2H4</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1810,24 +1810,24 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GMT25Z</t>
+          <t>GMD2H5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1837,24 +1837,24 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GMT2QF</t>
+          <t>GMD2HE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HE</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GMT2WL</t>
+          <t>GMD2HF</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2WL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HF</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>MT1060</t>
+          <t>GMD2HG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HG</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>MT1068</t>
+          <t>GMD2HH</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HH</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>MT2006</t>
+          <t>GMD2HJ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HJ</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>AEG225</t>
+          <t>GMD2HK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HK</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>AEG22R</t>
+          <t>GMD2MH</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs, ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>AEG233</t>
+          <t>GMD2MJ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>AEG26X</t>
+          <t>GMD2PA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Efter genomgång av kursen ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG26X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2PA</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>AEG29N</t>
+          <t>GMD3GZ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Efter godkänd kursen ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG29N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD3GZ</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>AEG2B6</t>
+          <t>MD1085</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2B6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>EG3007</t>
+          <t>MD1097</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>EG3009</t>
+          <t>MD1098</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>EG3012</t>
+          <t>MD1103</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1103</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>MD2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>EG3015</t>
+          <t>MD2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2024</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>EG3017</t>
+          <t>MD2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs, ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2025</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>EG3018</t>
+          <t>MD2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs, ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GEG26J</t>
+          <t>GMT228</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2355,19 +2355,19 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GEG2JP</t>
+          <t>GMT25Z</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2JP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GEG39Z</t>
+          <t>GMT2QF</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG39Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GEG3FY</t>
+          <t>GMT2WL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs, ska studenten kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3FY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2WL</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GSQ23K</t>
+          <t>MT1060</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2463,19 +2463,19 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GSQ25K</t>
+          <t>MT1068</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1068</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GSQ2DH</t>
+          <t>MT2006</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2517,19 +2517,19 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2DH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GSQ2J4</t>
+          <t>AEG225</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna: ·…</t>
+          <t>Efter genomgången kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2J4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GSQ2L8</t>
+          <t>AEG22R</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Efter genomgången…</t>
+          <t>Efter avslutad kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GSQ2L9</t>
+          <t>AEG233</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GSQ2MC</t>
+          <t>AEG26X</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter genomgång av kursen ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2MC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG26X</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GSQ2VY</t>
+          <t>AEG29N</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kursen ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2VY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG29N</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GSQ2WM</t>
+          <t>AEG2B6</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2WM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2B6</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GSQ33N</t>
+          <t>EG3007</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2706,19 +2706,19 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GST2CL</t>
+          <t>EG3009</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Efter kursen skall studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GST2CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>ST1013</t>
+          <t>EG3012</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Efter kursen skall studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ST1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>AMI22T</t>
+          <t>EG3014</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>AMI23A</t>
+          <t>EG3015</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter genomgången kurs skall studenten kunna…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>AMI23C</t>
+          <t>EG3017</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>AMI23G</t>
+          <t>EG3018</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Efter avslutad kursen ska studenten kunna:…</t>
+          <t>Efter avslutad kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>AMI23K</t>
+          <t>GEG26J</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>AMI23L</t>
+          <t>GEG2JP</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs kommer studenten att kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2JP</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GMI23G</t>
+          <t>GEG39Z</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG39Z</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GMI24H</t>
+          <t>GEG3FY</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI24H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3FY</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GMI26H</t>
+          <t>GSQ23K</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI26H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GMI2J3</t>
+          <t>GSQ25K</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2J3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GMI2MD</t>
+          <t>GSQ2DH</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Efter avslutad utbildning ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2MD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2DH</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>MI4001</t>
+          <t>GSQ2J4</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3079,44 +3079,584 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter genomgången kurs ska studenten kunna: ·…</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2J4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>GSQ2L8</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Efter genomgången…</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2L9</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2MC</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2MC</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2VY</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2VY</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2WM</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2WM</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>GSQ33N</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>GST2CL</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>STA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Efter kursen skall studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GST2CL</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>ST1013</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>STA</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Efter kursen skall studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ST1013</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>AMI22T</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22T</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>AMI23A</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>AMI23C</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23C</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>AMI23G</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Efter avslutad kursen ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23G</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>AMI23K</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23K</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>AMI23L</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs kommer studenten att kunna:…</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23L</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>GMI23G</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>GMI24H</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI24H</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>GMI26H</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI26H</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>GMI2J3</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2J3</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>GMI2MD</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Efter avslutad utbildning ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2MD</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>MI4001</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
           <t>MI4002</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>XYZ</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4002</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E99"/>
+  <autoFilter ref="A1:E119"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3314,6 +3854,46 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens.xlsx
@@ -2377,7 +2377,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">

--- a/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E119"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -634,7 +634,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>BY2025</t>
+          <t>BY3005</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenterna kunna:…</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY2025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY3005</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>BY3005</t>
+          <t>GBY2RN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -676,19 +676,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenterna kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2RN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GBY2RN</t>
+          <t>GBY2V5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2RN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2V5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GBY2V5</t>
+          <t>GBY2V8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -730,19 +730,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2V5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2V8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GBY2V8</t>
+          <t>GBY33L</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -762,14 +762,14 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2V8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY33L</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GBY33L</t>
+          <t>GBY34M</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -784,19 +784,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs skall den studerande kunna:…</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY33L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34M</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GBY34M</t>
+          <t>GBY34N</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs skall den studerande kunna:…</t>
+          <t>Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34N</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GBY34N</t>
+          <t>GBY38D</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -838,19 +838,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs skall studenten kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY38D</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GBY38D</t>
+          <t>GBY3AX</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande för ett konkret husbyggnadsprojekt kunna:…</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY38D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY3AX</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GBY3AX</t>
+          <t>GDT2JM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BYA</t>
+          <t>DTA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -892,19 +892,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande för ett konkret husbyggnadsprojekt kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY3AX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JM</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GDT2JM</t>
+          <t>GDT2JN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -924,14 +924,14 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GDT2JN</t>
+          <t>GDT34Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT34Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GDT34Z</t>
+          <t>ET1029</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DTA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT34Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ET1029</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ET1029</t>
+          <t>GIE36Z</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna:_…</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ET1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE36Z</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GIE26L</t>
+          <t>GIK28T</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GIE26M</t>
+          <t>GIK29B</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK29B</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GIE26N</t>
+          <t>GIK2Q3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1086,19 +1086,19 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2Q3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GIE2QS</t>
+          <t>GMA2EY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1113,19 +1113,19 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2QS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GIE2RF</t>
+          <t>GMD2BH</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2RF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2BH</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GIE36Z</t>
+          <t>GMD2EX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna:_…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE36Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2EX</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>IE1069</t>
+          <t>GMD2GU</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GU</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GIK28T</t>
+          <t>GMD2H2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GIK29B</t>
+          <t>GMD2H3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK29B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GIK2BD</t>
+          <t>GMD2H4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2BD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GIK2FB</t>
+          <t>GMD2H5</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2FB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GIK2Q3</t>
+          <t>GMD2HE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2Q3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HE</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GIK2QZ</t>
+          <t>GMD2HF</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2QZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HF</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GIK2UK</t>
+          <t>GMD2HG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Efter genomförd kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2UK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HG</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GIK2XJ</t>
+          <t>GMD2HH</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HH</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GIK2XK</t>
+          <t>GMD2HJ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1437,19 +1437,19 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HJ</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GIK2YP</t>
+          <t>GMD2HK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HK</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GIK2YR</t>
+          <t>GMD2MH</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GIK32K</t>
+          <t>GMD2MJ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GIK32L</t>
+          <t>GMD2PA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska den studerande…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2PA</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GIK32M</t>
+          <t>GMD3GZ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD3GZ</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GIK32N</t>
+          <t>MD1085</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GIK339</t>
+          <t>MD1097</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK339</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GMA2EY</t>
+          <t>MD1098</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1648,19 +1648,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GMD2BH</t>
+          <t>MD1103</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1680,14 +1680,14 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1103</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GMD2EX</t>
+          <t>MD2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1707,14 +1707,14 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2EX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GMD2GU</t>
+          <t>MD2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1734,14 +1734,14 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2024</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GMD2H2</t>
+          <t>MD2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1761,14 +1761,14 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2025</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GMD2H3</t>
+          <t>MD2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1788,19 +1788,19 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GMD2H4</t>
+          <t>GMT228</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1810,24 +1810,24 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GMD2H5</t>
+          <t>GMT25Z</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1837,24 +1837,24 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GMD2HE</t>
+          <t>GMT2QF</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GMD2HF</t>
+          <t>GMT2WL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2WL</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GMD2HG</t>
+          <t>MT1060</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GMD2HH</t>
+          <t>MT1068</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1068</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GMD2HJ</t>
+          <t>MT2006</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GMD2HK</t>
+          <t>AEG225</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GMD2MH</t>
+          <t>AEG22R</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GMD2MJ</t>
+          <t>AEG233</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GMD2PA</t>
+          <t>AEG26X</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande…</t>
+          <t>Efter genomgång av kursen ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2PA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG26X</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GMD3GZ</t>
+          <t>AEG29N</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kursen ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD3GZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG29N</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>MD1085</t>
+          <t>AEG2B6</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2B6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>MD1097</t>
+          <t>EG3007</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>MD1098</t>
+          <t>EG3009</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>MD1103</t>
+          <t>EG3012</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1103</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>MD2023</t>
+          <t>EG3014</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>MD2024</t>
+          <t>EG3015</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter genomgången kurs skall studenten kunna…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>MD2025</t>
+          <t>EG3017</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>MD2026</t>
+          <t>EG3018</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GMT228</t>
+          <t>GEG26J</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2355,19 +2355,19 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GMT25Z</t>
+          <t>GEG2JP</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2JP</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GMT2QF</t>
+          <t>GEG39Z</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG39Z</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GMT2WL</t>
+          <t>GEG3FY</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter godkänd kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2WL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3FY</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>MT1060</t>
+          <t>GSQ23K</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2463,19 +2463,19 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>MT1068</t>
+          <t>GSQ25K</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>MT2006</t>
+          <t>GSQ2DH</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2517,19 +2517,19 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2DH</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>AEG225</t>
+          <t>GSQ2J4</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna…</t>
+          <t>Efter genomgången kurs ska studenten kunna: ·…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2J4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>AEG22R</t>
+          <t>GSQ2L8</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs, ska studenten kunna:…</t>
+          <t>Efter genomgången…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>AEG233</t>
+          <t>GSQ2L9</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L9</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>AEG26X</t>
+          <t>GSQ2MC</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Efter genomgång av kursen ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG26X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2MC</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>AEG29N</t>
+          <t>GSQ2VY</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Efter godkänd kursen ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG29N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2VY</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>AEG2B6</t>
+          <t>GSQ2WM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs skall studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2B6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2WM</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>EG3007</t>
+          <t>GSQ33N</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2706,19 +2706,19 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>EG3009</t>
+          <t>GST2CL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>STA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter kursen skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GST2CL</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>EG3012</t>
+          <t>ST1013</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>STA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter kursen skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ST1013</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>AMI22T</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22T</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>EG3015</t>
+          <t>AMI23A</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>EG3017</t>
+          <t>AMI23C</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs, ska studenten kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23C</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>EG3018</t>
+          <t>AMI23G</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs, ska studenten kunna:…</t>
+          <t>Efter avslutad kursen ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23G</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GEG26J</t>
+          <t>AMI23K</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23K</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GEG2JP</t>
+          <t>AMI23L</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs kommer studenten att kunna:…</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2JP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23L</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GEG39Z</t>
+          <t>GMI23G</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG39Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GEG3FY</t>
+          <t>GMI24H</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs, ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3FY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI24H</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GSQ23K</t>
+          <t>GMI26H</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI26H</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GSQ25K</t>
+          <t>GMI2J3</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2J3</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GSQ2DH</t>
+          <t>GMI2MD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad utbildning ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2DH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2MD</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GSQ2J4</t>
+          <t>MI4001</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna: ·…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2J4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GSQ2L8</t>
+          <t>MI4002</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3106,557 +3106,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Efter genomgången…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L8</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2L9</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L9</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2MC</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2MC</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2VY</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2VY</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2WM</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2WM</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>GSQ33N</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>GST2CL</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>STA</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Efter kursen skall studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GST2CL</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>ST1013</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>STA</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Efter kursen skall studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ST1013</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>AMI22T</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22T</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>AMI23A</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>AMI23C</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23C</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>AMI23G</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Efter avslutad kursen ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23G</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>AMI23K</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23K</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>AMI23L</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs kommer studenten att kunna:…</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23L</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>GMI23G</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>GMI24H</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI24H</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>GMI26H</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI26H</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>GMI2J3</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2J3</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>GMI2MD</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Efter avslutad utbildning ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2MD</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>MI4001</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>MI4002</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4002</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E119"/>
+  <autoFilter ref="A1:E99"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3854,46 +3314,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$98</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -985,12 +985,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GIE36Z</t>
+          <t>GIK28T</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1000,19 +1000,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna:_…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE36Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GIK28T</t>
+          <t>GIK29B</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,19 +1027,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK29B</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GIK29B</t>
+          <t>GIK2Q3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1059,19 +1059,19 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK29B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2Q3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GIK2Q3</t>
+          <t>GMA2EY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1086,19 +1086,19 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2Q3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GMA2EY</t>
+          <t>GMD2BH</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1108,19 +1108,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2BH</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GMD2BH</t>
+          <t>GMD2EX</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1140,14 +1140,14 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2EX</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GMD2EX</t>
+          <t>GMD2GU</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2EX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GU</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GMD2GU</t>
+          <t>GMD2H2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GMD2H2</t>
+          <t>GMD2H3</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1221,14 +1221,14 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GMD2H3</t>
+          <t>GMD2H4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1248,14 +1248,14 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GMD2H4</t>
+          <t>GMD2H5</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1275,14 +1275,14 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GMD2H5</t>
+          <t>GMD2HE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1302,14 +1302,14 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HE</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GMD2HE</t>
+          <t>GMD2HF</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1329,14 +1329,14 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HF</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GMD2HF</t>
+          <t>GMD2HG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1356,14 +1356,14 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HG</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GMD2HG</t>
+          <t>GMD2HH</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1383,14 +1383,14 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HH</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GMD2HH</t>
+          <t>GMD2HJ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1410,14 +1410,14 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HJ</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GMD2HJ</t>
+          <t>GMD2HK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1437,14 +1437,14 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HK</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GMD2HK</t>
+          <t>GMD2MH</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1464,14 +1464,14 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GMD2MH</t>
+          <t>GMD2MJ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1491,14 +1491,14 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GMD2MJ</t>
+          <t>GMD2PA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2PA</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GMD2PA</t>
+          <t>GMD3GZ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1540,19 +1540,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2PA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD3GZ</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GMD3GZ</t>
+          <t>MD1085</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD3GZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>MD1085</t>
+          <t>MD1097</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1594,19 +1594,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>MD1097</t>
+          <t>MD1098</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1621,19 +1621,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>MD1098</t>
+          <t>MD1103</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1653,14 +1653,14 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1103</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>MD1103</t>
+          <t>MD2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1680,14 +1680,14 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1103</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>MD2023</t>
+          <t>MD2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1707,14 +1707,14 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2024</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>MD2024</t>
+          <t>MD2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1734,14 +1734,14 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2025</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>MD2025</t>
+          <t>MD2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1761,19 +1761,19 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>MD2026</t>
+          <t>GMT228</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GMT228</t>
+          <t>GMT25Z</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1810,19 +1810,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GMT25Z</t>
+          <t>GMT2QF</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GMT2QF</t>
+          <t>GMT2WL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1869,14 +1869,14 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2WL</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GMT2WL</t>
+          <t>MT1060</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1891,19 +1891,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2WL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>MT1060</t>
+          <t>MT1068</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1918,19 +1918,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1068</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>MT1068</t>
+          <t>MT2006</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>MT2006</t>
+          <t>AEG225</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1972,19 +1972,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>AEG225</t>
+          <t>AEG22R</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1999,19 +1999,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>AEG22R</t>
+          <t>AEG233</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2026,19 +2026,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs, ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>AEG233</t>
+          <t>AEG26X</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2053,19 +2053,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna…</t>
+          <t>Efter genomgång av kursen ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG26X</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>AEG26X</t>
+          <t>AEG29N</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2080,19 +2080,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Efter genomgång av kursen ska studenten kunna:…</t>
+          <t>Efter godkänd kursen ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG26X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG29N</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>AEG29N</t>
+          <t>AEG2B6</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2107,19 +2107,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Efter godkänd kursen ska studenten kunna:…</t>
+          <t>Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG29N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2B6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>AEG2B6</t>
+          <t>EG3007</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs skall studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2B6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>EG3007</t>
+          <t>EG3009</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2166,14 +2166,14 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>EG3009</t>
+          <t>EG3012</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2193,14 +2193,14 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>EG3012</t>
+          <t>EG3014</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2220,14 +2220,14 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>EG3015</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2242,19 +2242,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs skall studenten kunna…</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>EG3015</t>
+          <t>EG3017</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2269,19 +2269,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten kunna…</t>
+          <t>Efter avslutad kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>EG3017</t>
+          <t>EG3018</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2301,14 +2301,14 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>EG3018</t>
+          <t>GEG26J</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2323,19 +2323,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs, ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GEG26J</t>
+          <t>GEG2JP</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2JP</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GEG2JP</t>
+          <t>GEG39Z</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2377,19 +2377,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2JP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG39Z</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GEG39Z</t>
+          <t>GEG3FY</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs skall studenten kunna:…</t>
+          <t>Efter godkänd kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG39Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3FY</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GEG3FY</t>
+          <t>GSQ23K</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2431,19 +2431,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs, ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3FY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GSQ23K</t>
+          <t>GSQ25K</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2463,14 +2463,14 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GSQ25K</t>
+          <t>GSQ2DH</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2490,14 +2490,14 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2DH</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GSQ2DH</t>
+          <t>GSQ2J4</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2512,19 +2512,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna: ·…</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2DH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2J4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GSQ2J4</t>
+          <t>GSQ2L8</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna: ·…</t>
+          <t>Efter genomgången…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2J4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GSQ2L8</t>
+          <t>GSQ2L9</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2566,19 +2566,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Efter genomgången…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GSQ2L9</t>
+          <t>GSQ2MC</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2598,14 +2598,14 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2MC</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GSQ2MC</t>
+          <t>GSQ2VY</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2620,19 +2620,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2MC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2VY</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GSQ2VY</t>
+          <t>GSQ2WM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2647,19 +2647,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2VY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2WM</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GSQ2WM</t>
+          <t>GSQ33N</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2679,19 +2679,19 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2WM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GSQ33N</t>
+          <t>GST2CL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>STA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter kursen skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GST2CL</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GST2CL</t>
+          <t>ST1013</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2733,19 +2733,19 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GST2CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ST1013</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>ST1013</t>
+          <t>AMI22T</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2755,19 +2755,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Efter kursen skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ST1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22T</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>AMI22T</t>
+          <t>AMI23A</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2782,19 +2782,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>AMI23A</t>
+          <t>AMI23C</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2809,19 +2809,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23C</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>AMI23C</t>
+          <t>AMI23G</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2836,19 +2836,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kursen ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23G</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>AMI23G</t>
+          <t>AMI23K</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2863,19 +2863,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Efter avslutad kursen ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23K</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>AMI23K</t>
+          <t>AMI23L</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2890,19 +2890,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs kommer studenten att kunna:…</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23L</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>AMI23L</t>
+          <t>GMI23G</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2917,19 +2917,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs kommer studenten att kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GMI23G</t>
+          <t>GMI24H</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2944,19 +2944,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI24H</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GMI24H</t>
+          <t>GMI26H</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2971,19 +2971,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI24H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI26H</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GMI26H</t>
+          <t>GMI2J3</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2998,19 +2998,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI26H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2J3</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GMI2J3</t>
+          <t>GMI2MD</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3025,19 +3025,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad utbildning ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2J3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2MD</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GMI2MD</t>
+          <t>MI4001</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3052,19 +3052,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Efter avslutad utbildning ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2MD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>MI4001</t>
+          <t>MI4002</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3084,39 +3084,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>MI4002</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4002</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E99"/>
+  <autoFilter ref="A1:E98"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3312,8 +3285,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$106</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -958,12 +958,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ET1029</t>
+          <t>FEB222K</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>ENERGIBM</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska doktoranden kunna:…</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ET1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222K</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GIK28T</t>
+          <t>FEB222L</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>ENERGIBM</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska doktoranden kunna:…</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222L</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GIK29B</t>
+          <t>FEB222M</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>ENERGIBM</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska doktoranden kunna:…</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK29B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222M</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GIK2Q3</t>
+          <t>ET1029</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2Q3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ET1029</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GMA2EY</t>
+          <t>GIK28T</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GMD2BH</t>
+          <t>GIK29B</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK29B</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GMD2EX</t>
+          <t>GIK2Q3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2EX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2Q3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GMD2GU</t>
+          <t>GMA2EY</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1162,19 +1162,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GMD2H2</t>
+          <t>GMD2BH</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2BH</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GMD2H3</t>
+          <t>GMD2EX</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1221,14 +1221,14 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2EX</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GMD2H4</t>
+          <t>GMD2GU</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1248,14 +1248,14 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GU</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GMD2H5</t>
+          <t>GMD2H2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1275,14 +1275,14 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GMD2HE</t>
+          <t>GMD2H3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1302,14 +1302,14 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GMD2HF</t>
+          <t>GMD2H4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1329,14 +1329,14 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GMD2HG</t>
+          <t>GMD2H5</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1356,14 +1356,14 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GMD2HH</t>
+          <t>GMD2HE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1383,14 +1383,14 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HE</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GMD2HJ</t>
+          <t>GMD2HF</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1410,14 +1410,14 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HF</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GMD2HK</t>
+          <t>GMD2HG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1437,14 +1437,14 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HG</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GMD2MH</t>
+          <t>GMD2HH</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1464,14 +1464,14 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HH</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GMD2MJ</t>
+          <t>GMD2HJ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1491,14 +1491,14 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HJ</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GMD2PA</t>
+          <t>GMD2HK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2PA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HK</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GMD3GZ</t>
+          <t>GMD2MH</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1545,14 +1545,14 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD3GZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>MD1085</t>
+          <t>GMD2MJ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>MD1097</t>
+          <t>GMD2PA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1594,19 +1594,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2PA</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>MD1098</t>
+          <t>GMD3GZ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1626,14 +1626,14 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD3GZ</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>MD1103</t>
+          <t>MD1085</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1653,14 +1653,14 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1103</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>MD2023</t>
+          <t>MD1097</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>MD2024</t>
+          <t>MD1098</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1707,14 +1707,14 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>MD2025</t>
+          <t>MD1103</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1734,14 +1734,14 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1103</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>MD2026</t>
+          <t>MD2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1761,19 +1761,19 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GMT228</t>
+          <t>MD2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2024</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GMT25Z</t>
+          <t>MD2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1810,24 +1810,24 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2025</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GMT2QF</t>
+          <t>MD2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1837,24 +1837,24 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GMT2WL</t>
+          <t>FMI2222</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MIKRODAT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska doktoranden kunna:…</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2WL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2222</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>MT1060</t>
+          <t>FMI2223</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MIKRODAT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska doktoranden kunna:…</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2223</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>MT1068</t>
+          <t>FMI2224</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MIKRODAT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska doktoranden kunna:…</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2224</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>MT2006</t>
+          <t>FMI2229</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MIKRODAT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska doktoranden kunna:…</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2229</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>AEG225</t>
+          <t>MIKR002</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MIKRODAT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MIKR002</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>AEG22R</t>
+          <t>GMT228</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs, ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>AEG233</t>
+          <t>GMT25Z</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna…</t>
+          <t>Efter godkänd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>AEG26X</t>
+          <t>GMT2QF</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Efter genomgång av kursen ska studenten kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG26X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>AEG29N</t>
+          <t>GMT2WL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Efter godkänd kursen ska studenten kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG29N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2WL</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>AEG2B6</t>
+          <t>MT1060</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs skall studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2B6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>EG3007</t>
+          <t>MT1068</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1068</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>EG3009</t>
+          <t>MT2006</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2166,14 +2166,14 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>EG3012</t>
+          <t>AEG225</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2188,19 +2188,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>AEG22R</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2215,19 +2215,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>EG3015</t>
+          <t>AEG233</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2242,19 +2242,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten kunna…</t>
+          <t>Efter genomgången kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>EG3017</t>
+          <t>AEG26X</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2269,19 +2269,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs, ska studenten kunna:…</t>
+          <t>Efter genomgång av kursen ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG26X</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>EG3018</t>
+          <t>AEG29N</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2296,19 +2296,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs, ska studenten kunna:…</t>
+          <t>Efter godkänd kursen ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG29N</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GEG26J</t>
+          <t>AEG2B6</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2323,19 +2323,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2B6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GEG2JP</t>
+          <t>EG3007</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2355,14 +2355,14 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2JP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GEG39Z</t>
+          <t>EG3009</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2377,19 +2377,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs skall studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG39Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GEG3FY</t>
+          <t>EG3012</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs, ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3FY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GSQ23K</t>
+          <t>EG3014</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2436,19 +2436,19 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GSQ25K</t>
+          <t>EG3015</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs skall studenten kunna…</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GSQ2DH</t>
+          <t>EG3017</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2DH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GSQ2J4</t>
+          <t>EG3018</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna: ·…</t>
+          <t>Efter avslutad kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2J4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GSQ2L8</t>
+          <t>GEG26J</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Efter genomgången…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GSQ2L9</t>
+          <t>GEG2JP</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2571,19 +2571,19 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2JP</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GSQ2MC</t>
+          <t>GEG39Z</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2MC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG39Z</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GSQ2VY</t>
+          <t>GEG3FY</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2620,19 +2620,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2VY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3FY</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GSQ2WM</t>
+          <t>GSQ23K</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2652,14 +2652,14 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2WM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GSQ33N</t>
+          <t>GSQ25K</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2679,19 +2679,19 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GST2CL</t>
+          <t>GSQ2DH</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Efter kursen skall studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GST2CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2DH</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>ST1013</t>
+          <t>GSQ2J4</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Efter kursen skall studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna: ·…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ST1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2J4</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>AMI22T</t>
+          <t>GSQ2L8</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången…</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>AMI23A</t>
+          <t>GSQ2L9</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L9</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>AMI23C</t>
+          <t>GSQ2MC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2MC</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>AMI23G</t>
+          <t>GSQ2VY</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Efter avslutad kursen ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2VY</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>AMI23K</t>
+          <t>GSQ2WM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2WM</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>AMI23L</t>
+          <t>GSQ33N</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs kommer studenten att kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GMI23G</t>
+          <t>GST2CL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>STA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter kursen skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GST2CL</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GMI24H</t>
+          <t>ST1013</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>STA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2944,19 +2944,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter kursen skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI24H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ST1013</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GMI26H</t>
+          <t>AMI22T</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2976,14 +2976,14 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI26H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22T</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GMI2J3</t>
+          <t>AMI23A</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2998,19 +2998,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2J3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GMI2MD</t>
+          <t>AMI23C</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3025,19 +3025,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Efter avslutad utbildning ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2MD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23C</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>MI4001</t>
+          <t>AMI23G</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3052,44 +3052,260 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter avslutad kursen ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23G</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>AMI23K</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23K</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>AMI23L</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs kommer studenten att kunna:…</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23L</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>GMI23G</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>GMI24H</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI24H</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>GMI26H</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI26H</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>GMI2J3</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2J3</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>GMI2MD</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Efter avslutad utbildning ska den studerande kunna:…</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2MD</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>MI4001</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
           <t>MI4002</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>XYZ</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4002</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E98"/>
+  <autoFilter ref="A1:E106"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3285,6 +3501,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -958,12 +958,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>FEB222K</t>
+          <t>ET1029</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ENERGIBM</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska doktoranden kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ET1029</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>FEB222L</t>
+          <t>GIK28T</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ENERGIBM</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska doktoranden kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>FEB222M</t>
+          <t>GIK29B</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ENERGIBM</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska doktoranden kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK29B</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ET1029</t>
+          <t>GIK2Q3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ET1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2Q3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GIK28T</t>
+          <t>GMA2EY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GIK29B</t>
+          <t>GMD2BH</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK29B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2BH</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GIK2Q3</t>
+          <t>GMD2EX</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2Q3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2EX</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GMA2EY</t>
+          <t>GMD2GU</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1162,19 +1162,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GU</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GMD2BH</t>
+          <t>GMD2H2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GMD2EX</t>
+          <t>GMD2H3</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1221,14 +1221,14 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2EX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GMD2GU</t>
+          <t>GMD2H4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1248,14 +1248,14 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GMD2H2</t>
+          <t>GMD2H5</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1275,14 +1275,14 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GMD2H3</t>
+          <t>GMD2HE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1302,14 +1302,14 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HE</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GMD2H4</t>
+          <t>GMD2HF</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1329,14 +1329,14 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HF</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GMD2H5</t>
+          <t>GMD2HG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1356,14 +1356,14 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HG</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GMD2HE</t>
+          <t>GMD2HH</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1383,14 +1383,14 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HH</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GMD2HF</t>
+          <t>GMD2HJ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1410,14 +1410,14 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HJ</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GMD2HG</t>
+          <t>GMD2HK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1437,14 +1437,14 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HK</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GMD2HH</t>
+          <t>GMD2MH</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1464,14 +1464,14 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GMD2HJ</t>
+          <t>GMD2MJ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1491,14 +1491,14 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GMD2HK</t>
+          <t>GMD2PA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2PA</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GMD2MH</t>
+          <t>GMD3GZ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1545,14 +1545,14 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD3GZ</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GMD2MJ</t>
+          <t>MD1085</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GMD2PA</t>
+          <t>MD1097</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1594,19 +1594,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2PA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GMD3GZ</t>
+          <t>MD1098</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1626,14 +1626,14 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD3GZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>MD1085</t>
+          <t>MD1103</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1653,14 +1653,14 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1103</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>MD1097</t>
+          <t>MD2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>MD1098</t>
+          <t>MD2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1707,14 +1707,14 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2024</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>MD1103</t>
+          <t>MD2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1734,14 +1734,14 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1103</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2025</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>MD2023</t>
+          <t>MD2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1761,19 +1761,19 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>MD2024</t>
+          <t>MIKR002</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MIKRODAT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MIKR002</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>MD2025</t>
+          <t>GMT228</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1810,24 +1810,24 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>MD2026</t>
+          <t>GMT25Z</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1837,24 +1837,24 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>FMI2222</t>
+          <t>GMT2QF</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MIKRODAT</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska doktoranden kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2222</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>FMI2223</t>
+          <t>GMT2WL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MIKRODAT</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska doktoranden kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2223</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2WL</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>FMI2224</t>
+          <t>MT1060</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MIKRODAT</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska doktoranden kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2224</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>FMI2229</t>
+          <t>MT1068</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MIKRODAT</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska doktoranden kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2229</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1068</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>MIKR002</t>
+          <t>MT2006</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MIKRODAT</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MIKR002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GMT228</t>
+          <t>AEG225</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GMT25Z</t>
+          <t>AEG22R</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GMT2QF</t>
+          <t>AEG233</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GMT2WL</t>
+          <t>AEG26X</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter genomgång av kursen ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2WL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG26X</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>MT1060</t>
+          <t>AEG29N</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kursen ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG29N</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>MT1068</t>
+          <t>AEG2B6</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2B6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>MT2006</t>
+          <t>EG3007</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2166,14 +2166,14 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>AEG225</t>
+          <t>EG3009</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2188,19 +2188,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>AEG22R</t>
+          <t>EG3012</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2215,19 +2215,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs, ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>AEG233</t>
+          <t>EG3014</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2242,19 +2242,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>AEG26X</t>
+          <t>EG3015</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2269,19 +2269,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Efter genomgång av kursen ska studenten kunna:…</t>
+          <t>Efter genomgången kurs skall studenten kunna…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG26X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>AEG29N</t>
+          <t>EG3017</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2296,19 +2296,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Efter godkänd kursen ska studenten kunna:…</t>
+          <t>Efter avslutad kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG29N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>AEG2B6</t>
+          <t>EG3018</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2323,19 +2323,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2B6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>EG3007</t>
+          <t>GEG26J</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>EG3009</t>
+          <t>GEG2JP</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2382,14 +2382,14 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2JP</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>EG3012</t>
+          <t>GEG39Z</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,19 +2404,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG39Z</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>GEG3FY</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3FY</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>EG3015</t>
+          <t>GSQ23K</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten kunna…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>EG3017</t>
+          <t>GSQ25K</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs, ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>EG3018</t>
+          <t>GSQ2DH</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs, ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2DH</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GEG26J</t>
+          <t>GSQ2J4</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna: ·…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2J4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GEG2JP</t>
+          <t>GSQ2L8</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter genomgången…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2JP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GEG39Z</t>
+          <t>GSQ2L9</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs skall studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG39Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L9</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GEG3FY</t>
+          <t>GSQ2MC</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2620,19 +2620,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs, ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3FY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2MC</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GSQ23K</t>
+          <t>GSQ2VY</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2647,19 +2647,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2VY</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GSQ25K</t>
+          <t>GSQ2WM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2679,14 +2679,14 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2WM</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GSQ2DH</t>
+          <t>GSQ33N</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2706,19 +2706,19 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2DH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GSQ2J4</t>
+          <t>GST2CL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>STA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna: ·…</t>
+          <t>Efter kursen skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2J4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GST2CL</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GSQ2L8</t>
+          <t>ST1013</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>STA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Efter genomgången…</t>
+          <t>Efter kursen skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ST1013</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GSQ2L9</t>
+          <t>AMI22T</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22T</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GSQ2MC</t>
+          <t>AMI23A</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2MC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GSQ2VY</t>
+          <t>AMI23C</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2VY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23C</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GSQ2WM</t>
+          <t>AMI23G</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kursen ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2WM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23G</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GSQ33N</t>
+          <t>AMI23K</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23K</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GST2CL</t>
+          <t>AMI23L</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2917,24 +2917,24 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Efter kursen skall studenten kunna:…</t>
+          <t>Efter avslutad kurs kommer studenten att kunna:…</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GST2CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23L</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>ST1013</t>
+          <t>GMI23G</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2944,19 +2944,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Efter kursen skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ST1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>AMI22T</t>
+          <t>GMI24H</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2971,19 +2971,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI24H</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>AMI23A</t>
+          <t>GMI26H</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2998,19 +2998,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI26H</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>AMI23C</t>
+          <t>GMI2J3</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3025,19 +3025,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2J3</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>AMI23G</t>
+          <t>GMI2MD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3052,19 +3052,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Efter avslutad kursen ska studenten kunna:…</t>
+          <t>Efter avslutad utbildning ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2MD</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>AMI23K</t>
+          <t>MI4001</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3084,14 +3084,14 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>AMI23L</t>
+          <t>MI4002</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3106,206 +3106,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs kommer studenten att kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23L</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>GMI23G</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>GMI24H</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI24H</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>GMI26H</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI26H</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>GMI2J3</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2J3</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>GMI2MD</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Efter avslutad utbildning ska den studerande kunna:…</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2MD</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>MI4001</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>MI4002</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4002</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E106"/>
+  <autoFilter ref="A1:E99"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3503,20 +3314,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$100</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1066,7 +1066,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GMA2EY</t>
+          <t>BMA229</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1086,19 +1086,19 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BMA229</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GMD2BH</t>
+          <t>GMA2EY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1108,19 +1108,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2BH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GMD2EX</t>
+          <t>GMD2BH</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1140,14 +1140,14 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2EX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2BH</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GMD2GU</t>
+          <t>GMD2EX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2EX</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GMD2H2</t>
+          <t>GMD2GU</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GU</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GMD2H3</t>
+          <t>GMD2H2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1221,14 +1221,14 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GMD2H4</t>
+          <t>GMD2H3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1248,14 +1248,14 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GMD2H5</t>
+          <t>GMD2H4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1275,14 +1275,14 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GMD2HE</t>
+          <t>GMD2H5</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1302,14 +1302,14 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GMD2HF</t>
+          <t>GMD2HE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1329,14 +1329,14 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HE</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GMD2HG</t>
+          <t>GMD2HF</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1356,14 +1356,14 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HF</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GMD2HH</t>
+          <t>GMD2HG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1383,14 +1383,14 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HG</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GMD2HJ</t>
+          <t>GMD2HH</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1410,14 +1410,14 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HH</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GMD2HK</t>
+          <t>GMD2HJ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1437,14 +1437,14 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HJ</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GMD2MH</t>
+          <t>GMD2HK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1464,14 +1464,14 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HK</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GMD2MJ</t>
+          <t>GMD2MH</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1491,14 +1491,14 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GMD2PA</t>
+          <t>GMD2MJ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2PA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GMD3GZ</t>
+          <t>GMD2PA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1540,19 +1540,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD3GZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2PA</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>MD1085</t>
+          <t>GMD3GZ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD3GZ</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>MD1097</t>
+          <t>MD1085</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1594,19 +1594,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>MD1098</t>
+          <t>MD1097</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1621,19 +1621,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>MD1103</t>
+          <t>MD1098</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1653,14 +1653,14 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1103</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>MD2023</t>
+          <t>MD1103</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1680,14 +1680,14 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1103</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>MD2024</t>
+          <t>MD2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1707,14 +1707,14 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>MD2025</t>
+          <t>MD2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1734,14 +1734,14 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2024</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>MD2026</t>
+          <t>MD2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1761,19 +1761,19 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2025</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>MIKR002</t>
+          <t>MD2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MIKRODAT</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MIKR002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GMT228</t>
+          <t>MIKR002</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MIKRODAT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1810,19 +1810,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MIKR002</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GMT25Z</t>
+          <t>GMT228</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GMT2QF</t>
+          <t>GMT25Z</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1864,19 +1864,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter godkänd kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GMT2WL</t>
+          <t>GMT2QF</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1896,14 +1896,14 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2WL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>MT1060</t>
+          <t>GMT2WL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1918,19 +1918,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2WL</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>MT1068</t>
+          <t>MT1060</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1945,19 +1945,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>MT2006</t>
+          <t>MT1068</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1068</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>AEG225</t>
+          <t>MT2006</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1999,19 +1999,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>AEG22R</t>
+          <t>AEG225</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2026,19 +2026,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs, ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>AEG233</t>
+          <t>AEG22R</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2053,19 +2053,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>AEG26X</t>
+          <t>AEG233</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2080,19 +2080,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Efter genomgång av kursen ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG26X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>AEG29N</t>
+          <t>AEG26X</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2107,19 +2107,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Efter godkänd kursen ska studenten kunna:…</t>
+          <t>Efter genomgång av kursen ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG29N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG26X</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>AEG2B6</t>
+          <t>AEG29N</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs skall studenten kunna:…</t>
+          <t>Efter godkänd kursen ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2B6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG29N</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>EG3007</t>
+          <t>AEG2B6</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2161,19 +2161,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2B6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>EG3009</t>
+          <t>EG3007</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2193,14 +2193,14 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>EG3012</t>
+          <t>EG3009</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2220,14 +2220,14 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>EG3012</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2247,14 +2247,14 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>EG3015</t>
+          <t>EG3014</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2269,19 +2269,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs skall studenten kunna…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>EG3017</t>
+          <t>EG3015</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2296,19 +2296,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs, ska studenten kunna:…</t>
+          <t>Efter genomgången kurs skall studenten kunna…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>EG3018</t>
+          <t>EG3017</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2328,14 +2328,14 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GEG26J</t>
+          <t>EG3018</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GEG2JP</t>
+          <t>GEG26J</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2377,19 +2377,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2JP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GEG39Z</t>
+          <t>GEG2JP</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,19 +2404,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs skall studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG39Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2JP</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GEG3FY</t>
+          <t>GEG39Z</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Efter godkänd kurs, ska studenten kunna:…</t>
+          <t>Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3FY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG39Z</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GSQ23K</t>
+          <t>GEG3FY</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2458,19 +2458,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter godkänd kurs, ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3FY</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GSQ25K</t>
+          <t>GSQ23K</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2490,14 +2490,14 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GSQ2DH</t>
+          <t>GSQ25K</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2517,14 +2517,14 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2DH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GSQ2J4</t>
+          <t>GSQ2DH</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna: ·…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2J4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2DH</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GSQ2L8</t>
+          <t>GSQ2J4</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2566,19 +2566,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Efter genomgången…</t>
+          <t>Efter genomgången kurs ska studenten kunna: ·…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2J4</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GSQ2L9</t>
+          <t>GSQ2L8</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2593,19 +2593,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter genomgången…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GSQ2MC</t>
+          <t>GSQ2L9</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2625,14 +2625,14 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2MC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L9</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GSQ2VY</t>
+          <t>GSQ2MC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2647,19 +2647,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2VY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2MC</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GSQ2WM</t>
+          <t>GSQ2VY</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2674,19 +2674,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Efter genomgången kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2WM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2VY</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GSQ33N</t>
+          <t>GSQ2WM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2706,19 +2706,19 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2WM</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GST2CL</t>
+          <t>GSQ33N</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2728,19 +2728,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Efter kursen skall studenten kunna:…</t>
+          <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GST2CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>ST1013</t>
+          <t>GST2CL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2760,19 +2760,19 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ST1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GST2CL</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>AMI22T</t>
+          <t>ST1013</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>STA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2782,19 +2782,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter kursen skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ST1013</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>AMI23A</t>
+          <t>AMI22T</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2809,19 +2809,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22T</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>AMI23C</t>
+          <t>AMI23A</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2836,19 +2836,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs skall studenten kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>AMI23G</t>
+          <t>AMI23C</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2863,19 +2863,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Efter avslutad kursen ska studenten kunna:…</t>
+          <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23C</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>AMI23K</t>
+          <t>AMI23G</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2890,19 +2890,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter avslutad kursen ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23G</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>AMI23L</t>
+          <t>AMI23K</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2917,19 +2917,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs kommer studenten att kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23K</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GMI23G</t>
+          <t>AMI23L</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2944,19 +2944,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs kommer studenten att kunna:…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23L</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GMI24H</t>
+          <t>GMI23G</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2971,19 +2971,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI24H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GMI26H</t>
+          <t>GMI24H</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2998,19 +2998,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI26H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI24H</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GMI2J3</t>
+          <t>GMI26H</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3025,19 +3025,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska den studerande kunna…</t>
+          <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2J3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI26H</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GMI2MD</t>
+          <t>GMI2J3</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3052,19 +3052,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Efter avslutad utbildning ska den studerande kunna:…</t>
+          <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2MD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2J3</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>MI4001</t>
+          <t>GMI2MD</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3079,44 +3079,71 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Efter avslutad kurs ska studenten kunna…</t>
+          <t>Efter avslutad utbildning ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2MD</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>MI4001</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Efter avslutad kurs ska studenten kunna…</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
           <t>MI4002</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>XYZ</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4002</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E99"/>
+  <autoFilter ref="A1:E100"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3314,6 +3341,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$E$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens'!$A$1:$G$100</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+          <t>2019-02-21</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABY22V</t>
         </is>
@@ -509,15 +527,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>2019-02-21</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABY22W</t>
         </is>
@@ -536,15 +560,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenterna kunna:…</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABY27W</t>
         </is>
@@ -563,15 +593,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska studenterna kunna:…</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABY2BL</t>
         </is>
@@ -590,15 +626,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+          <t>2013-03-14</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1047</t>
         </is>
@@ -617,15 +659,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+          <t>2014-08-28</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1054</t>
         </is>
@@ -644,15 +692,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+          <t>2017-12-14</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenterna kunna:…</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY3005</t>
         </is>
@@ -671,15 +725,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+          <t>2021-08-24</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2RN</t>
         </is>
@@ -698,15 +758,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2V5</t>
         </is>
@@ -725,15 +791,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2V8</t>
         </is>
@@ -752,15 +824,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+          <t>2023-03-07</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY33L</t>
         </is>
@@ -779,15 +857,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+          <t>2023-05-23</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Efter godkänd kurs skall den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34M</t>
         </is>
@@ -806,15 +890,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+          <t>2023-05-23</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34N</t>
         </is>
@@ -833,15 +923,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY38D</t>
         </is>
@@ -860,15 +956,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande för ett konkret husbyggnadsprojekt kunna:…</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY3AX</t>
         </is>
@@ -887,15 +989,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JM</t>
         </is>
@@ -914,15 +1022,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JN</t>
         </is>
@@ -941,15 +1055,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT34Z</t>
         </is>
@@ -968,15 +1088,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+          <t>2018-02-13</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ET1029</t>
         </is>
@@ -995,15 +1121,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+          <t>2018-10-11</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
         </is>
@@ -1022,15 +1154,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+          <t>2019-04-29</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK29B</t>
         </is>
@@ -1049,15 +1187,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+          <t>2021-05-20</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2Q3</t>
         </is>
@@ -1076,15 +1220,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BMA229</t>
         </is>
@@ -1103,15 +1253,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+          <t>2020-03-04</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
         </is>
@@ -1130,15 +1286,25 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2019-08-29</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2019-09-19</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2BH</t>
         </is>
@@ -1157,15 +1323,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+          <t>2020-02-25</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2EX</t>
         </is>
@@ -1184,15 +1356,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-06-04</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>2020-06-15</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GU</t>
         </is>
@@ -1211,15 +1393,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
         </is>
@@ -1238,15 +1426,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-06-08</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H3</t>
         </is>
@@ -1265,15 +1463,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H4</t>
         </is>
@@ -1292,15 +1496,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-06-08</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H5</t>
         </is>
@@ -1319,15 +1533,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>2020-09-15</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HE</t>
         </is>
@@ -1346,15 +1570,25 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HF</t>
         </is>
@@ -1373,15 +1607,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>2020-09-15</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HG</t>
         </is>
@@ -1400,15 +1644,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HH</t>
         </is>
@@ -1427,15 +1681,25 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HJ</t>
         </is>
@@ -1454,15 +1718,25 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HK</t>
         </is>
@@ -1481,15 +1755,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-02-23</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
         </is>
@@ -1508,15 +1792,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-02-23</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
         </is>
@@ -1535,15 +1829,25 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>2021-04-14</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande…</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2PA</t>
         </is>
@@ -1562,15 +1866,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD3GZ</t>
         </is>
@@ -1589,15 +1899,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+          <t>2013-12-17</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
         </is>
@@ -1616,15 +1932,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+          <t>2015-03-05</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
         </is>
@@ -1643,15 +1965,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+          <t>2015-03-05</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
         </is>
@@ -1670,15 +1998,25 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2015-10-01</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>2021-12-03</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1103</t>
         </is>
@@ -1697,15 +2035,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
+          <t>2017-09-28</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
         </is>
@@ -1724,15 +2068,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+          <t>2017-09-28</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2024</t>
         </is>
@@ -1751,15 +2101,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+          <t>2017-09-28</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2025</t>
         </is>
@@ -1778,15 +2134,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+          <t>2017-09-28</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2026</t>
         </is>
@@ -1805,15 +2167,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
+          <t>2012-12-04</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MIKR002</t>
         </is>
@@ -1832,15 +2200,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
+          <t>2018-04-05</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
         </is>
@@ -1859,15 +2233,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+          <t>2019-01-31</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>Efter godkänd kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
         </is>
@@ -1886,15 +2266,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
+          <t>2021-05-20</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
         </is>
@@ -1913,15 +2299,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
+          <t>2022-06-08</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2WL</t>
         </is>
@@ -1940,15 +2332,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
+          <t>2014-04-03</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
         </is>
@@ -1967,15 +2365,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
+          <t>2016-05-19</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1068</t>
         </is>
@@ -1994,15 +2398,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
+          <t>2007-05-22</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
         </is>
@@ -2021,15 +2431,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
+          <t>2018-05-24</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna…</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
         </is>
@@ -2048,15 +2464,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
+          <t>2019-01-31</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>Efter avslutad kurs, ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
         </is>
@@ -2075,15 +2497,21 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
+          <t>2019-06-05</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna…</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
         </is>
@@ -2102,15 +2530,21 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
+          <t>2021-05-20</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>Efter genomgång av kursen ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG26X</t>
         </is>
@@ -2129,15 +2563,21 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>Efter godkänd kursen ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG29N</t>
         </is>
@@ -2156,15 +2596,21 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2B6</t>
         </is>
@@ -2183,15 +2629,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+          <t>2015-08-27</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
         </is>
@@ -2210,15 +2662,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
+          <t>2015-09-17</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
         </is>
@@ -2237,15 +2695,21 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
+          <t>2015-09-17</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
         </is>
@@ -2264,15 +2728,21 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
+          <t>2015-08-27</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
         </is>
@@ -2291,15 +2761,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
+          <t>2015-08-27</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>Efter genomgången kurs skall studenten kunna…</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
         </is>
@@ -2318,15 +2794,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
+          <t>2016-09-22</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>Efter avslutad kurs, ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
         </is>
@@ -2345,15 +2827,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+          <t>2016-09-22</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>Efter avslutad kurs, ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
         </is>
@@ -2372,15 +2860,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
+          <t>2019-02-21</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
         </is>
@@ -2399,15 +2893,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2JP</t>
         </is>
@@ -2426,15 +2926,21 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
+          <t>2024-02-05</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>Efter godkänd kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG39Z</t>
         </is>
@@ -2453,15 +2959,21 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>Efter godkänd kurs, ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3FY</t>
         </is>
@@ -2480,15 +2992,21 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
+          <t>2018-06-14</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
         </is>
@@ -2507,15 +3025,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
+          <t>2018-11-08</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
         </is>
@@ -2534,15 +3058,21 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
+          <t>2020-02-06</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2DH</t>
         </is>
@@ -2561,15 +3091,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
+          <t>2020-09-03</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna: ·…</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2J4</t>
         </is>
@@ -2588,15 +3124,21 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
+          <t>2020-12-17</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>Efter genomgången…</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L8</t>
         </is>
@@ -2615,15 +3157,21 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
+          <t>2020-12-17</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L9</t>
         </is>
@@ -2642,15 +3190,21 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
+          <t>2021-02-18</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2MC</t>
         </is>
@@ -2669,15 +3223,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
+          <t>2022-03-24</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2VY</t>
         </is>
@@ -2696,15 +3256,21 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
+          <t>2022-06-08</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2WM</t>
         </is>
@@ -2723,15 +3289,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
+          <t>2023-03-07</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>Efter genomgången kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
         </is>
@@ -2750,15 +3322,21 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
+          <t>2020-01-30</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>Efter kursen skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GST2CL</t>
         </is>
@@ -2777,15 +3355,25 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2010-12-14</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t>2013-02-13</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t>Efter kursen skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ST1013</t>
         </is>
@@ -2804,15 +3392,21 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
+          <t>2019-02-21</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22T</t>
         </is>
@@ -2831,15 +3425,21 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
+          <t>2019-08-29</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
         </is>
@@ -2858,15 +3458,21 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
+          <t>2019-08-29</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>Efter avslutad kurs skall studenten kunna:…</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23C</t>
         </is>
@@ -2885,15 +3491,21 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
+          <t>2019-10-17</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>Efter avslutad kursen ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23G</t>
         </is>
@@ -2912,15 +3524,21 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
+          <t>2019-10-17</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23K</t>
         </is>
@@ -2939,15 +3557,21 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
+          <t>2019-10-17</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>Efter avslutad kurs kommer studenten att kunna:…</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23L</t>
         </is>
@@ -2966,15 +3590,21 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
+          <t>2018-06-14</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
         </is>
@@ -2993,15 +3623,21 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
+          <t>2018-09-13</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI24H</t>
         </is>
@@ -3020,15 +3656,21 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
+          <t>2019-02-21</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI26H</t>
         </is>
@@ -3047,15 +3689,21 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
+          <t>2020-09-03</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska den studerande kunna…</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2J3</t>
         </is>
@@ -3074,15 +3722,21 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
+          <t>2021-02-18</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>Efter avslutad utbildning ska den studerande kunna:…</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2MD</t>
         </is>
@@ -3101,15 +3755,25 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
+          <t>2011-02-15</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t>2012-11-07</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
         </is>
@@ -3128,221 +3792,227 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avviker från referensformen</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
+          <t>2011-12-08</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Avviker från referensformen</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>Efter avslutad kurs ska studenten kunna…</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4002</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E100"/>
+  <autoFilter ref="A1:G100"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId192"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId198"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
